--- a/TextGame project/Assets/Resources/Story/1.xlsx
+++ b/TextGame project/Assets/Resources/Story/1.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Text-Game\TextGame project\Assets\Resources\Story\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83F87B9C-70EF-4364-8EC8-260E9E222FD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F06990F-48D2-47B7-AC32-B187DF717218}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3108" yWindow="5340" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1776" yWindow="3504" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="OLE_LINK1" localSheetId="0">Sheet1!$B$2</definedName>
+    <definedName name="OLE_LINK1" localSheetId="0">Sheet1!$B$3</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="16">
   <si>
     <t>旁白</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -62,6 +62,30 @@
   </si>
   <si>
     <t>White</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Avatar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vocal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BgImg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bgm</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -397,79 +421,105 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="34.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C2" t="s">
         <v>9</v>
-      </c>
-      <c r="D1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
       </c>
       <c r="D2" t="s">
         <v>4</v>
       </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C6" t="s">
         <v>9</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D6" t="s">
         <v>4</v>
       </c>
     </row>

--- a/TextGame project/Assets/Resources/Story/1.xlsx
+++ b/TextGame project/Assets/Resources/Story/1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Text-Game\TextGame project\Assets\Resources\Story\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F06990F-48D2-47B7-AC32-B187DF717218}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8334925-53F2-4227-BA27-4C3F44CCF813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1776" yWindow="3504" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="38">
   <si>
     <t>旁白</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -44,10 +44,6 @@
     <t>终于到周五了～明天可以好好睡个懒觉！</t>
   </si>
   <si>
-    <t>Null</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Qianye</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -87,13 +83,89 @@
   <si>
     <t>Bgm</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Character1Action</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Character1Img</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Character2Action</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Character2Img</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Character3Action</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Character3Img</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>disappear</t>
+  </si>
+  <si>
+    <t>appearAt(x, y)</t>
+  </si>
+  <si>
+    <t>千叶</t>
+  </si>
+  <si>
+    <t>旁白</t>
+  </si>
+  <si>
+    <t>（她往下翻帖子）</t>
+  </si>
+  <si>
+    <t>（千叶的眼睛亮了起来）</t>
+  </si>
+  <si>
+    <t>（她站起来，走到窗边，望向远处的方向）</t>
+  </si>
+  <si>
+    <t>反正周末也没事做... 要不，去看看？</t>
+  </si>
+  <si>
+    <t>（她想了想，又有点犹豫）</t>
+  </si>
+  <si>
+    <t>可是... 会不会真的很危险啊？</t>
+  </si>
+  <si>
+    <t>怕什么！不就是个废弃学校嘛，大不了白天去，看一眼就回来。</t>
+  </si>
+  <si>
+    <t>临渊高中... 就是郊区那所废弃了好久的学校吗？</t>
+  </si>
+  <si>
+    <t>"有人说晚上看到里面有灯光"、"路过的时候听到了奇怪的声音"、"十年前那里有个女生失踪了"...</t>
+  </si>
+  <si>
+    <t>哇，听起来好刺激啊！</t>
+  </si>
+  <si>
+    <t>（她甩了甩头）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>（她把手机塞进口袋，背起书包）</t>
+  </si>
+  <si>
+    <t>好，就这么决定了！明天去探险！</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -114,6 +186,12 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9.8000000000000007"/>
+      <color rgb="FFC9A26D"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -136,11 +214,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -421,33 +503,57 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:L19"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="2" max="2" width="34.109375" customWidth="1"/>
+    <col min="7" max="7" width="15.88671875" customWidth="1"/>
+    <col min="8" max="8" width="13.6640625" customWidth="1"/>
+    <col min="9" max="9" width="15.77734375" customWidth="1"/>
+    <col min="10" max="10" width="13.21875" customWidth="1"/>
+    <col min="11" max="11" width="16.21875" customWidth="1"/>
+    <col min="12" max="12" width="13.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" t="s">
         <v>10</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>11</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>12</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>13</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>14</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -455,10 +561,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -466,8 +569,20 @@
       <c r="F2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -475,51 +590,183 @@
         <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="I3" s="2"/>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6" t="s">
         <v>0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" t="s">
         <v>4</v>
       </c>
     </row>

--- a/TextGame project/Assets/Resources/Story/1.xlsx
+++ b/TextGame project/Assets/Resources/Story/1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Text-Game\TextGame project\Assets\Resources\Story\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8334925-53F2-4227-BA27-4C3F44CCF813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96D2092B-FFFE-4D73-A10C-82B46EAF5889}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,6 +17,8 @@
   </sheets>
   <definedNames>
     <definedName name="OLE_LINK1" localSheetId="0">Sheet1!$B$3</definedName>
+    <definedName name="OLE_LINK2" localSheetId="0">Sheet1!$B$24</definedName>
+    <definedName name="OLE_LINK3" localSheetId="0">Sheet1!$B$40</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="64">
   <si>
     <t>旁白</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -54,9 +56,6 @@
     <t>嗯？这是什么...</t>
   </si>
   <si>
-    <t>（手机屏幕上是学校论坛的帖子，标题写着：「你们听说了吗？废弃的临渊高中最近闹鬼了」）</t>
-  </si>
-  <si>
     <t>White</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -85,80 +84,170 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Character1Action</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Character1Img</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Character2Action</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Character2Img</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Character3Action</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Character3Img</t>
+    <t>千叶</t>
+  </si>
+  <si>
+    <t>旁白</t>
+  </si>
+  <si>
+    <t>（她往下翻帖子）</t>
+  </si>
+  <si>
+    <t>（千叶的眼睛亮了起来）</t>
+  </si>
+  <si>
+    <t>（她站起来，走到窗边，望向远处的方向）</t>
+  </si>
+  <si>
+    <t>反正周末也没事做... 要不，去看看？</t>
+  </si>
+  <si>
+    <t>（她想了想，又有点犹豫）</t>
+  </si>
+  <si>
+    <t>可是... 会不会真的很危险啊？</t>
+  </si>
+  <si>
+    <t>怕什么！不就是个废弃学校嘛，大不了白天去，看一眼就回来。</t>
+  </si>
+  <si>
+    <t>临渊高中... 就是郊区那所废弃了好久的学校吗？</t>
+  </si>
+  <si>
+    <t>"有人说晚上看到里面有灯光"、"路过的时候听到了奇怪的声音"、"十年前那里有个女生失踪了"...</t>
+  </si>
+  <si>
+    <t>哇，听起来好刺激啊！</t>
+  </si>
+  <si>
+    <t>（她甩了甩头）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>（她把手机塞进口袋，背起书包）</t>
+  </si>
+  <si>
+    <t>好，就这么决定了！明天去探险！</t>
+  </si>
+  <si>
+    <t>（手机屏幕上是学校论坛的帖子，标题写着：[你们听说了吗？废弃的临渊高中最近闹鬼了]）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Action1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Character1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>x1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Action2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>x2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Character2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Action3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>x3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Character3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>appearAt</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>disappear</t>
   </si>
   <si>
-    <t>appearAt(x, y)</t>
-  </si>
-  <si>
-    <t>千叶</t>
-  </si>
-  <si>
-    <t>旁白</t>
-  </si>
-  <si>
-    <t>（她往下翻帖子）</t>
-  </si>
-  <si>
-    <t>（千叶的眼睛亮了起来）</t>
-  </si>
-  <si>
-    <t>（她站起来，走到窗边，望向远处的方向）</t>
-  </si>
-  <si>
-    <t>反正周末也没事做... 要不，去看看？</t>
-  </si>
-  <si>
-    <t>（她想了想，又有点犹豫）</t>
-  </si>
-  <si>
-    <t>可是... 会不会真的很危险啊？</t>
-  </si>
-  <si>
-    <t>怕什么！不就是个废弃学校嘛，大不了白天去，看一眼就回来。</t>
-  </si>
-  <si>
-    <t>临渊高中... 就是郊区那所废弃了好久的学校吗？</t>
-  </si>
-  <si>
-    <t>"有人说晚上看到里面有灯光"、"路过的时候听到了奇怪的声音"、"十年前那里有个女生失踪了"...</t>
-  </si>
-  <si>
-    <t>哇，听起来好刺激啊！</t>
-  </si>
-  <si>
-    <t>（她甩了甩头）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>（她把手机塞进口袋，背起书包）</t>
-  </si>
-  <si>
-    <t>好，就这么决定了！明天去探险！</t>
+    <t>（千叶走在上学的路上，一边走一边踢着小石子）</t>
+  </si>
+  <si>
+    <t>（这时，旁边传来一个声音）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>王叔叔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>千叶，去上学啊？</t>
+  </si>
+  <si>
+    <t>Wangshushu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>（千叶转过头，看到隔壁的王叔叔正站在他家门口，笑着看着她）</t>
+  </si>
+  <si>
+    <t>王叔叔早！</t>
+  </si>
+  <si>
+    <t>早啊。看你今天心情不错，有什么开心的事吗？</t>
+  </si>
+  <si>
+    <t>没什么啦，就是想到周末了，有点开心。</t>
+  </si>
+  <si>
+    <t>哈哈，年轻人就是好啊。周末有什么打算吗？</t>
+  </si>
+  <si>
+    <t>嗯... 还没想好呢，可能在家写作业吧。</t>
+  </si>
+  <si>
+    <t>（她没说要去废弃学校的事，觉得说了可能会被骂）</t>
+  </si>
+  <si>
+    <t>（若有所思)这样啊...</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>（他顿了顿，语气变得 "关心" 起来）</t>
+  </si>
+  <si>
+    <t>千叶啊，王叔叔提醒你一句，最近别往偏僻的地方跑，尤其是郊区那边，不太安全。</t>
+  </si>
+  <si>
+    <t>啊？为什么啊？</t>
+  </si>
+  <si>
+    <t>最近附近不太太平，你一个女孩子，要注意安全。知道吗？</t>
+  </si>
+  <si>
+    <t>哦... 知道了，谢谢王叔叔。</t>
+  </si>
+  <si>
+    <t>嗯，乖。快去吧，别迟到了。</t>
+  </si>
+  <si>
+    <t>王叔叔再见！</t>
+  </si>
+  <si>
+    <t>（千叶跑走了）</t>
+  </si>
+  <si>
+    <t>（王叔叔站在原地，看着千叶的背影，脸上的笑容慢慢消失了，眼神变得阴冷）</t>
+  </si>
+  <si>
+    <t>... 快了，就快了。</t>
   </si>
 </sst>
 </file>
@@ -503,57 +592,67 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:O40"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="2" max="2" width="34.109375" customWidth="1"/>
+    <col min="2" max="2" width="66.5546875" customWidth="1"/>
     <col min="7" max="7" width="15.88671875" customWidth="1"/>
     <col min="8" max="8" width="13.6640625" customWidth="1"/>
     <col min="9" max="9" width="15.77734375" customWidth="1"/>
     <col min="10" max="10" width="13.21875" customWidth="1"/>
     <col min="11" max="11" width="16.21875" customWidth="1"/>
     <col min="12" max="12" width="13.33203125" customWidth="1"/>
+    <col min="15" max="15" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" t="s">
         <v>9</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>10</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>11</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>12</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>13</v>
       </c>
-      <c r="F1" t="s">
-        <v>14</v>
-      </c>
       <c r="G1" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H1" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="I1" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="J1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="K1" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="L1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
+        <v>35</v>
+      </c>
+      <c r="M1" t="s">
+        <v>36</v>
+      </c>
+      <c r="N1" t="s">
+        <v>37</v>
+      </c>
+      <c r="O1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -561,7 +660,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -570,19 +669,18 @@
         <v>1</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H2" t="s">
-        <v>4</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+        <v>39</v>
+      </c>
+      <c r="H2">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="I2" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -594,7 +692,7 @@
       </c>
       <c r="I3" s="2"/>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:15">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -602,10 +700,10 @@
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -616,158 +714,416 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:15">
       <c r="A6" t="s">
         <v>0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="C7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:15">
       <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="1" t="s">
+      <c r="C11" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="A11" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="A12" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" s="1" t="s">
+      <c r="C16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
-      <c r="A13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="1" t="s">
+      <c r="C18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C13" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
-      <c r="A14" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
-      <c r="A15" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
-      <c r="A16" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" t="s">
-        <v>23</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C17" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" t="s">
-        <v>24</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="C19" t="s">
         <v>4</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20">
+        <v>2</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H20">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="I20" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" t="s">
+        <v>7</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="K21">
+        <v>819.16989999999998</v>
+      </c>
+      <c r="L21" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="A26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C26" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="A27" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C27" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
+      <c r="A28" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C28" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
+      <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C29" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
+      <c r="A30" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C30" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
+      <c r="A31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C31" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
+      <c r="A32" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" t="s">
+        <v>14</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C33" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C34" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" t="s">
+        <v>14</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C35" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C36" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" t="s">
+        <v>14</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C37" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C38" t="s">
+        <v>7</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C40" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/TextGame project/Assets/Resources/Story/1.xlsx
+++ b/TextGame project/Assets/Resources/Story/1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Text-Game\TextGame project\Assets\Resources\Story\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A517AD1-FE57-46F1-A3D2-CA0C4CB341B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29585D02-808B-433E-B5B6-8567A207E165}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="135">
   <si>
     <t>旁白</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -461,6 +461,18 @@
   </si>
   <si>
     <t>（她站在原地，不知道该怎么办）</t>
+  </si>
+  <si>
+    <t>choice</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>choice1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>choice2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -805,7 +817,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q107"/>
+  <dimension ref="A1:Q108"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="2" max="2" width="66.5546875" customWidth="1"/>
@@ -2012,7 +2024,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="97" spans="1:3">
+    <row r="97" spans="1:5">
       <c r="A97" t="s">
         <v>2</v>
       </c>
@@ -2023,7 +2035,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="98" spans="1:3">
+    <row r="98" spans="1:5">
       <c r="A98" t="s">
         <v>99</v>
       </c>
@@ -2034,7 +2046,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="99" spans="1:3">
+    <row r="99" spans="1:5">
       <c r="A99" t="s">
         <v>0</v>
       </c>
@@ -2045,7 +2057,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="100" spans="1:3">
+    <row r="100" spans="1:5">
       <c r="A100" t="s">
         <v>2</v>
       </c>
@@ -2056,7 +2068,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="101" spans="1:3">
+    <row r="101" spans="1:5">
       <c r="A101" t="s">
         <v>99</v>
       </c>
@@ -2067,7 +2079,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="102" spans="1:3">
+    <row r="102" spans="1:5">
       <c r="A102" t="s">
         <v>2</v>
       </c>
@@ -2078,7 +2090,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="103" spans="1:3">
+    <row r="103" spans="1:5">
       <c r="A103" t="s">
         <v>0</v>
       </c>
@@ -2089,7 +2101,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="104" spans="1:3">
+    <row r="104" spans="1:5">
       <c r="A104" t="s">
         <v>2</v>
       </c>
@@ -2100,7 +2112,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="105" spans="1:3">
+    <row r="105" spans="1:5">
       <c r="A105" t="s">
         <v>99</v>
       </c>
@@ -2111,7 +2123,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="106" spans="1:3">
+    <row r="106" spans="1:5">
       <c r="A106" t="s">
         <v>2</v>
       </c>
@@ -2122,7 +2134,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="107" spans="1:3">
+    <row r="107" spans="1:5">
       <c r="A107" t="s">
         <v>0</v>
       </c>
@@ -2131,6 +2143,23 @@
       </c>
       <c r="C107" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5">
+      <c r="A108" t="s">
+        <v>132</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C108">
+        <v>2</v>
+      </c>
+      <c r="D108" t="s">
+        <v>134</v>
+      </c>
+      <c r="E108">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/TextGame project/Assets/Resources/Story/1.xlsx
+++ b/TextGame project/Assets/Resources/Story/1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Text-Game\TextGame project\Assets\Resources\Story\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29585D02-808B-433E-B5B6-8567A207E165}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28459669-F1FD-4AE4-9467-8D96710D1C3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/TextGame project/Assets/Resources/Story/1.xlsx
+++ b/TextGame project/Assets/Resources/Story/1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Text-Game\TextGame project\Assets\Resources\Story\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\share\Text-Game\TextGame project\Assets\Resources\Story\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28459669-F1FD-4AE4-9467-8D96710D1C3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F37E2EFD-61E8-4342-9883-80304A40BD35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -818,16 +818,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q108"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.15"/>
   <cols>
-    <col min="2" max="2" width="66.5546875" customWidth="1"/>
-    <col min="7" max="7" width="15.88671875" customWidth="1"/>
-    <col min="8" max="8" width="13.6640625" customWidth="1"/>
-    <col min="9" max="9" width="15.77734375" customWidth="1"/>
-    <col min="10" max="10" width="13.21875" customWidth="1"/>
-    <col min="11" max="11" width="16.21875" customWidth="1"/>
-    <col min="12" max="12" width="13.33203125" customWidth="1"/>
-    <col min="15" max="15" width="13.6640625" customWidth="1"/>
+    <col min="2" max="2" width="66.5703125" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" customWidth="1"/>
+    <col min="8" max="8" width="13.640625" customWidth="1"/>
+    <col min="9" max="9" width="15.78515625" customWidth="1"/>
+    <col min="10" max="10" width="13.2109375" customWidth="1"/>
+    <col min="11" max="11" width="16.2109375" customWidth="1"/>
+    <col min="12" max="12" width="13.35546875" customWidth="1"/>
+    <col min="15" max="15" width="13.640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
@@ -928,9 +928,6 @@
       </c>
       <c r="C4" t="s">
         <v>6</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
       </c>
       <c r="K4" s="2"/>
     </row>

--- a/TextGame project/Assets/Resources/Story/1.xlsx
+++ b/TextGame project/Assets/Resources/Story/1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\share\Text-Game\TextGame project\Assets\Resources\Story\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Text-Game\TextGame project\Assets\Resources\Story\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F37E2EFD-61E8-4342-9883-80304A40BD35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{429D00DE-B799-4879-9C80-0B6C9E6ACCF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="140">
   <si>
     <t>旁白</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -473,6 +473,24 @@
   <si>
     <t>choice2</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LastBGImg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LastBGM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LastX1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LastX2</t>
+  </si>
+  <si>
+    <t>LastX3</t>
   </si>
 </sst>
 </file>
@@ -817,20 +835,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q108"/>
-  <sheetFormatPr defaultRowHeight="14.15"/>
+  <dimension ref="A1:V108"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="2" max="2" width="66.5703125" customWidth="1"/>
-    <col min="7" max="7" width="15.85546875" customWidth="1"/>
-    <col min="8" max="8" width="13.640625" customWidth="1"/>
-    <col min="9" max="9" width="15.78515625" customWidth="1"/>
-    <col min="10" max="10" width="13.2109375" customWidth="1"/>
-    <col min="11" max="11" width="16.2109375" customWidth="1"/>
-    <col min="12" max="12" width="13.35546875" customWidth="1"/>
-    <col min="15" max="15" width="13.640625" customWidth="1"/>
+    <col min="2" max="2" width="66.5546875" customWidth="1"/>
+    <col min="7" max="7" width="15.88671875" customWidth="1"/>
+    <col min="8" max="8" width="13.6640625" customWidth="1"/>
+    <col min="9" max="9" width="15.77734375" customWidth="1"/>
+    <col min="10" max="10" width="13.21875" customWidth="1"/>
+    <col min="11" max="11" width="16.21875" customWidth="1"/>
+    <col min="12" max="12" width="13.33203125" customWidth="1"/>
+    <col min="15" max="15" width="13.6640625" customWidth="1"/>
+    <col min="17" max="17" width="11.77734375" customWidth="1"/>
+    <col min="18" max="18" width="11.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:22">
       <c r="A1" t="s">
         <v>7</v>
       </c>
@@ -882,8 +902,23 @@
       <c r="Q1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="2" spans="1:17">
+      <c r="R1" t="s">
+        <v>135</v>
+      </c>
+      <c r="S1" t="s">
+        <v>136</v>
+      </c>
+      <c r="T1" t="s">
+        <v>137</v>
+      </c>
+      <c r="U1" t="s">
+        <v>138</v>
+      </c>
+      <c r="V1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22">
       <c r="G2" s="2" t="s">
         <v>38</v>
       </c>
@@ -891,7 +926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:22">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -919,7 +954,7 @@
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:22">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -930,8 +965,17 @@
         <v>6</v>
       </c>
       <c r="K4" s="2"/>
-    </row>
-    <row r="5" spans="1:17">
+      <c r="R4">
+        <v>1</v>
+      </c>
+      <c r="T4">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U4">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -941,8 +985,17 @@
       <c r="C5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:17">
+      <c r="R5">
+        <v>1</v>
+      </c>
+      <c r="T5">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U5">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -952,8 +1005,17 @@
       <c r="C6" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="7" spans="1:17">
+      <c r="R6">
+        <v>1</v>
+      </c>
+      <c r="T6">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U6">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22">
       <c r="A7" t="s">
         <v>2</v>
       </c>
@@ -963,8 +1025,17 @@
       <c r="C7" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="1:17">
+      <c r="R7">
+        <v>1</v>
+      </c>
+      <c r="T7">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U7">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22">
       <c r="A8" t="s">
         <v>0</v>
       </c>
@@ -974,8 +1045,17 @@
       <c r="C8" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="9" spans="1:17">
+      <c r="R8">
+        <v>1</v>
+      </c>
+      <c r="T8">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U8">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -985,8 +1065,17 @@
       <c r="C9" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:17">
+      <c r="R9">
+        <v>1</v>
+      </c>
+      <c r="T9">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U9">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -996,8 +1085,17 @@
       <c r="C10" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="11" spans="1:17">
+      <c r="R10">
+        <v>1</v>
+      </c>
+      <c r="T10">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U10">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -1007,8 +1105,17 @@
       <c r="C11" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="12" spans="1:17">
+      <c r="R11">
+        <v>1</v>
+      </c>
+      <c r="T11">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U11">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -1018,8 +1125,17 @@
       <c r="C12" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="13" spans="1:17">
+      <c r="R12">
+        <v>1</v>
+      </c>
+      <c r="T12">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U12">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -1029,8 +1145,17 @@
       <c r="C13" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="14" spans="1:17">
+      <c r="R13">
+        <v>1</v>
+      </c>
+      <c r="T13">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U13">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -1040,8 +1165,17 @@
       <c r="C14" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="15" spans="1:17">
+      <c r="R14">
+        <v>1</v>
+      </c>
+      <c r="T14">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U14">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -1051,8 +1185,17 @@
       <c r="C15" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:17">
+      <c r="R15">
+        <v>1</v>
+      </c>
+      <c r="T15">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U15">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -1062,8 +1205,17 @@
       <c r="C16" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="17" spans="1:14">
+      <c r="R16">
+        <v>1</v>
+      </c>
+      <c r="T16">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U16">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -1073,8 +1225,17 @@
       <c r="C17" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="1:14">
+      <c r="R17">
+        <v>1</v>
+      </c>
+      <c r="T17">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U17">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21">
       <c r="A18" t="s">
         <v>14</v>
       </c>
@@ -1084,8 +1245,17 @@
       <c r="C18" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="19" spans="1:14">
+      <c r="R18">
+        <v>1</v>
+      </c>
+      <c r="T18">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U18">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21">
       <c r="A19" t="s">
         <v>13</v>
       </c>
@@ -1095,8 +1265,17 @@
       <c r="C19" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="20" spans="1:14">
+      <c r="R19">
+        <v>1</v>
+      </c>
+      <c r="T19">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U19">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21">
       <c r="A20" t="s">
         <v>14</v>
       </c>
@@ -1106,8 +1285,17 @@
       <c r="C20" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="21" spans="1:14">
+      <c r="R20">
+        <v>1</v>
+      </c>
+      <c r="T20">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U20">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21">
       <c r="A21" t="s">
         <v>13</v>
       </c>
@@ -1118,8 +1306,17 @@
         <v>4</v>
       </c>
       <c r="I21" s="2"/>
-    </row>
-    <row r="22" spans="1:14">
+      <c r="R21">
+        <v>1</v>
+      </c>
+      <c r="T21">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U21">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21">
       <c r="A22" t="s">
         <v>14</v>
       </c>
@@ -1142,8 +1339,17 @@
       <c r="N22" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="23" spans="1:14">
+      <c r="R22">
+        <v>1</v>
+      </c>
+      <c r="T22">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U22">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21">
       <c r="A23" t="s">
         <v>14</v>
       </c>
@@ -1153,8 +1359,17 @@
       <c r="C23" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="24" spans="1:14">
+      <c r="R23">
+        <v>2</v>
+      </c>
+      <c r="T23">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U23">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21">
       <c r="A24" t="s">
         <v>42</v>
       </c>
@@ -1164,8 +1379,17 @@
       <c r="C24" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="25" spans="1:14">
+      <c r="R24">
+        <v>2</v>
+      </c>
+      <c r="T24">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U24">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21">
       <c r="A25" t="s">
         <v>14</v>
       </c>
@@ -1175,8 +1399,17 @@
       <c r="C25" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="26" spans="1:14">
+      <c r="R25">
+        <v>2</v>
+      </c>
+      <c r="T25">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U25">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21">
       <c r="A26" t="s">
         <v>13</v>
       </c>
@@ -1186,8 +1419,17 @@
       <c r="C26" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="1:14">
+      <c r="R26">
+        <v>2</v>
+      </c>
+      <c r="T26">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U26">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21">
       <c r="A27" t="s">
         <v>42</v>
       </c>
@@ -1197,8 +1439,17 @@
       <c r="C27" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="28" spans="1:14">
+      <c r="R27">
+        <v>2</v>
+      </c>
+      <c r="T27">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U27">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21">
       <c r="A28" t="s">
         <v>13</v>
       </c>
@@ -1208,8 +1459,17 @@
       <c r="C28" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="29" spans="1:14">
+      <c r="R28">
+        <v>2</v>
+      </c>
+      <c r="T28">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U28">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21">
       <c r="A29" t="s">
         <v>42</v>
       </c>
@@ -1219,8 +1479,17 @@
       <c r="C29" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="30" spans="1:14">
+      <c r="R29">
+        <v>2</v>
+      </c>
+      <c r="T29">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U29">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21">
       <c r="A30" t="s">
         <v>13</v>
       </c>
@@ -1230,8 +1499,17 @@
       <c r="C30" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="31" spans="1:14">
+      <c r="R30">
+        <v>2</v>
+      </c>
+      <c r="T30">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U30">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21">
       <c r="A31" t="s">
         <v>14</v>
       </c>
@@ -1241,8 +1519,17 @@
       <c r="C31" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="32" spans="1:14">
+      <c r="R31">
+        <v>2</v>
+      </c>
+      <c r="T31">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U31">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21">
       <c r="A32" t="s">
         <v>42</v>
       </c>
@@ -1252,8 +1539,17 @@
       <c r="C32" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="33" spans="1:12">
+      <c r="R32">
+        <v>2</v>
+      </c>
+      <c r="T32">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U32">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21">
       <c r="A33" t="s">
         <v>14</v>
       </c>
@@ -1263,8 +1559,17 @@
       <c r="C33" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="34" spans="1:12">
+      <c r="R33">
+        <v>2</v>
+      </c>
+      <c r="T33">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U33">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21">
       <c r="A34" t="s">
         <v>42</v>
       </c>
@@ -1274,8 +1579,17 @@
       <c r="C34" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="35" spans="1:12">
+      <c r="R34">
+        <v>2</v>
+      </c>
+      <c r="T34">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U34">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21">
       <c r="A35" t="s">
         <v>13</v>
       </c>
@@ -1285,8 +1599,17 @@
       <c r="C35" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="36" spans="1:12">
+      <c r="R35">
+        <v>2</v>
+      </c>
+      <c r="T35">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U35">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21">
       <c r="A36" t="s">
         <v>42</v>
       </c>
@@ -1296,8 +1619,17 @@
       <c r="C36" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="37" spans="1:12">
+      <c r="R36">
+        <v>2</v>
+      </c>
+      <c r="T36">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U36">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21">
       <c r="A37" t="s">
         <v>13</v>
       </c>
@@ -1307,8 +1639,17 @@
       <c r="C37" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="38" spans="1:12">
+      <c r="R37">
+        <v>2</v>
+      </c>
+      <c r="T37">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U37">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21">
       <c r="A38" t="s">
         <v>42</v>
       </c>
@@ -1318,8 +1659,17 @@
       <c r="C38" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="39" spans="1:12">
+      <c r="R38">
+        <v>2</v>
+      </c>
+      <c r="T38">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U38">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21">
       <c r="A39" t="s">
         <v>13</v>
       </c>
@@ -1329,8 +1679,17 @@
       <c r="C39" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="40" spans="1:12">
+      <c r="R39">
+        <v>2</v>
+      </c>
+      <c r="T39">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U39">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21">
       <c r="A40" t="s">
         <v>14</v>
       </c>
@@ -1343,8 +1702,17 @@
       <c r="I40" s="2" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="41" spans="1:12">
+      <c r="R40">
+        <v>2</v>
+      </c>
+      <c r="T40">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U40">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21">
       <c r="A41" t="s">
         <v>14</v>
       </c>
@@ -1354,8 +1722,17 @@
       <c r="C41" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="42" spans="1:12">
+      <c r="R41">
+        <v>2</v>
+      </c>
+      <c r="T41">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U41">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21">
       <c r="A42" t="s">
         <v>42</v>
       </c>
@@ -1365,8 +1742,17 @@
       <c r="C42" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="43" spans="1:12">
+      <c r="R42">
+        <v>2</v>
+      </c>
+      <c r="T42">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U42">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21">
       <c r="A43" t="s">
         <v>42</v>
       </c>
@@ -1385,8 +1771,17 @@
       <c r="L43" s="2" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="44" spans="1:12">
+      <c r="R43">
+        <v>2</v>
+      </c>
+      <c r="T43">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U43">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21">
       <c r="A44" t="s">
         <v>14</v>
       </c>
@@ -1411,8 +1806,17 @@
       <c r="K44" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="1:12">
+      <c r="R44">
+        <v>2</v>
+      </c>
+      <c r="T44">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U44">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21">
       <c r="A45" t="s">
         <v>13</v>
       </c>
@@ -1422,8 +1826,17 @@
       <c r="C45" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="1:12">
+      <c r="R45">
+        <v>3</v>
+      </c>
+      <c r="T45">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U45">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21">
       <c r="A46" t="s">
         <v>14</v>
       </c>
@@ -1433,8 +1846,17 @@
       <c r="C46" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="47" spans="1:12">
+      <c r="R46">
+        <v>3</v>
+      </c>
+      <c r="T46">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U46">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21">
       <c r="A47" t="s">
         <v>13</v>
       </c>
@@ -1444,8 +1866,17 @@
       <c r="C47" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="1:12">
+      <c r="R47">
+        <v>3</v>
+      </c>
+      <c r="T47">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U47">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21">
       <c r="A48" t="s">
         <v>14</v>
       </c>
@@ -1455,8 +1886,17 @@
       <c r="C48" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="49" spans="1:11">
+      <c r="R48">
+        <v>3</v>
+      </c>
+      <c r="T48">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U48">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="49" spans="1:21">
       <c r="A49" t="s">
         <v>13</v>
       </c>
@@ -1466,8 +1906,17 @@
       <c r="C49" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="1:11">
+      <c r="R49">
+        <v>3</v>
+      </c>
+      <c r="T49">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U49">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21">
       <c r="A50" t="s">
         <v>14</v>
       </c>
@@ -1477,8 +1926,17 @@
       <c r="C50" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="51" spans="1:11">
+      <c r="R50">
+        <v>3</v>
+      </c>
+      <c r="T50">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U50">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="51" spans="1:21">
       <c r="A51" t="s">
         <v>2</v>
       </c>
@@ -1488,8 +1946,17 @@
       <c r="C51" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="52" spans="1:11">
+      <c r="R51">
+        <v>3</v>
+      </c>
+      <c r="T51">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U51">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="52" spans="1:21">
       <c r="A52" t="s">
         <v>14</v>
       </c>
@@ -1499,8 +1966,17 @@
       <c r="C52" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="53" spans="1:11">
+      <c r="R52">
+        <v>3</v>
+      </c>
+      <c r="T52">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U52">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="53" spans="1:21">
       <c r="A53" t="s">
         <v>2</v>
       </c>
@@ -1510,8 +1986,17 @@
       <c r="C53" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="54" spans="1:11">
+      <c r="R53">
+        <v>3</v>
+      </c>
+      <c r="T53">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U53">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="54" spans="1:21">
       <c r="A54" t="s">
         <v>0</v>
       </c>
@@ -1524,8 +2009,17 @@
       <c r="I54" s="2" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="55" spans="1:11">
+      <c r="R54">
+        <v>3</v>
+      </c>
+      <c r="T54">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U54">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="55" spans="1:21">
       <c r="A55" t="s">
         <v>0</v>
       </c>
@@ -1547,8 +2041,17 @@
       <c r="K55" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="56" spans="1:11">
+      <c r="R55">
+        <v>3</v>
+      </c>
+      <c r="T55">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U55">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="56" spans="1:21">
       <c r="A56" t="s">
         <v>2</v>
       </c>
@@ -1558,8 +2061,17 @@
       <c r="C56" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="57" spans="1:11">
+      <c r="R56">
+        <v>4</v>
+      </c>
+      <c r="T56">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U56">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="57" spans="1:21">
       <c r="A57" t="s">
         <v>0</v>
       </c>
@@ -1569,8 +2081,17 @@
       <c r="C57" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="58" spans="1:11">
+      <c r="R57">
+        <v>4</v>
+      </c>
+      <c r="T57">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U57">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21">
       <c r="A58" t="s">
         <v>0</v>
       </c>
@@ -1580,8 +2101,17 @@
       <c r="C58" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="59" spans="1:11">
+      <c r="R58">
+        <v>4</v>
+      </c>
+      <c r="T58">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U58">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21">
       <c r="A59" t="s">
         <v>2</v>
       </c>
@@ -1591,8 +2121,17 @@
       <c r="C59" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="1:11">
+      <c r="R59">
+        <v>4</v>
+      </c>
+      <c r="T59">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U59">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="60" spans="1:21">
       <c r="A60" t="s">
         <v>0</v>
       </c>
@@ -1602,8 +2141,17 @@
       <c r="C60" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="61" spans="1:11">
+      <c r="R60">
+        <v>4</v>
+      </c>
+      <c r="T60">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U60">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="61" spans="1:21">
       <c r="A61" t="s">
         <v>2</v>
       </c>
@@ -1613,8 +2161,17 @@
       <c r="C61" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="62" spans="1:11">
+      <c r="R61">
+        <v>4</v>
+      </c>
+      <c r="T61">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U61">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="62" spans="1:21">
       <c r="A62" t="s">
         <v>0</v>
       </c>
@@ -1624,8 +2181,17 @@
       <c r="C62" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="63" spans="1:11">
+      <c r="R62">
+        <v>4</v>
+      </c>
+      <c r="T62">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U62">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="63" spans="1:21">
       <c r="A63" t="s">
         <v>0</v>
       </c>
@@ -1635,8 +2201,17 @@
       <c r="C63" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="64" spans="1:11">
+      <c r="R63">
+        <v>4</v>
+      </c>
+      <c r="T63">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U63">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="64" spans="1:21">
       <c r="A64" t="s">
         <v>2</v>
       </c>
@@ -1646,8 +2221,17 @@
       <c r="C64" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="65" spans="1:15">
+      <c r="R64">
+        <v>4</v>
+      </c>
+      <c r="T64">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U64">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="65" spans="1:21">
       <c r="A65" t="s">
         <v>0</v>
       </c>
@@ -1657,8 +2241,17 @@
       <c r="C65" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="66" spans="1:15">
+      <c r="R65">
+        <v>4</v>
+      </c>
+      <c r="T65">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U65">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="66" spans="1:21">
       <c r="A66" t="s">
         <v>0</v>
       </c>
@@ -1668,8 +2261,17 @@
       <c r="C66" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="67" spans="1:15">
+      <c r="R66">
+        <v>4</v>
+      </c>
+      <c r="T66">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U66">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="67" spans="1:21">
       <c r="A67" t="s">
         <v>2</v>
       </c>
@@ -1679,8 +2281,17 @@
       <c r="C67" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="68" spans="1:15">
+      <c r="R67">
+        <v>4</v>
+      </c>
+      <c r="T67">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U67">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="68" spans="1:21">
       <c r="A68" t="s">
         <v>0</v>
       </c>
@@ -1690,8 +2301,17 @@
       <c r="C68" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="69" spans="1:15">
+      <c r="R68">
+        <v>4</v>
+      </c>
+      <c r="T68">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U68">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="69" spans="1:21">
       <c r="A69" t="s">
         <v>0</v>
       </c>
@@ -1701,8 +2321,17 @@
       <c r="C69" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="70" spans="1:15">
+      <c r="R69">
+        <v>4</v>
+      </c>
+      <c r="T69">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U69">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="70" spans="1:21">
       <c r="A70" t="s">
         <v>2</v>
       </c>
@@ -1712,8 +2341,17 @@
       <c r="C70" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="71" spans="1:15">
+      <c r="R70">
+        <v>4</v>
+      </c>
+      <c r="T70">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U70">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="71" spans="1:21">
       <c r="A71" t="s">
         <v>0</v>
       </c>
@@ -1723,8 +2361,17 @@
       <c r="C71" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="72" spans="1:15">
+      <c r="R71">
+        <v>4</v>
+      </c>
+      <c r="T71">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U71">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="72" spans="1:21">
       <c r="A72" t="s">
         <v>0</v>
       </c>
@@ -1734,8 +2381,17 @@
       <c r="C72" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="73" spans="1:15">
+      <c r="R72">
+        <v>4</v>
+      </c>
+      <c r="T72">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U72">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="73" spans="1:21">
       <c r="A73" t="s">
         <v>0</v>
       </c>
@@ -1755,8 +2411,17 @@
         <v>101</v>
       </c>
       <c r="O73" s="2"/>
-    </row>
-    <row r="74" spans="1:15">
+      <c r="R73">
+        <v>4</v>
+      </c>
+      <c r="T73">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U73">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="74" spans="1:21">
       <c r="A74" t="s">
         <v>2</v>
       </c>
@@ -1766,8 +2431,17 @@
       <c r="C74" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="75" spans="1:15">
+      <c r="R74">
+        <v>4</v>
+      </c>
+      <c r="T74">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U74">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="75" spans="1:21">
       <c r="A75" t="s">
         <v>0</v>
       </c>
@@ -1780,8 +2454,17 @@
       <c r="I75" s="2" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="76" spans="1:15">
+      <c r="R75">
+        <v>4</v>
+      </c>
+      <c r="T75">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U75">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="76" spans="1:21">
       <c r="A76" t="s">
         <v>0</v>
       </c>
@@ -1791,8 +2474,17 @@
       <c r="C76" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="77" spans="1:15">
+      <c r="R76">
+        <v>4</v>
+      </c>
+      <c r="T76">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U76">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="77" spans="1:21">
       <c r="A77" t="s">
         <v>99</v>
       </c>
@@ -1802,8 +2494,17 @@
       <c r="C77" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="78" spans="1:15">
+      <c r="R77">
+        <v>4</v>
+      </c>
+      <c r="T77">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U77">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="78" spans="1:21">
       <c r="A78" t="s">
         <v>0</v>
       </c>
@@ -1813,8 +2514,17 @@
       <c r="C78" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="79" spans="1:15">
+      <c r="R78">
+        <v>4</v>
+      </c>
+      <c r="T78">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U78">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="79" spans="1:21">
       <c r="A79" t="s">
         <v>99</v>
       </c>
@@ -1824,8 +2534,17 @@
       <c r="C79" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="80" spans="1:15">
+      <c r="R79">
+        <v>4</v>
+      </c>
+      <c r="T79">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U79">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="80" spans="1:21">
       <c r="A80" t="s">
         <v>0</v>
       </c>
@@ -1844,8 +2563,17 @@
       <c r="K80" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="81" spans="1:3">
+      <c r="R80">
+        <v>4</v>
+      </c>
+      <c r="T80">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U80">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="81" spans="1:21">
       <c r="A81" t="s">
         <v>0</v>
       </c>
@@ -1855,8 +2583,17 @@
       <c r="C81" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="82" spans="1:3">
+      <c r="R81">
+        <v>4</v>
+      </c>
+      <c r="T81">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U81">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="82" spans="1:21">
       <c r="A82" t="s">
         <v>2</v>
       </c>
@@ -1866,8 +2603,17 @@
       <c r="C82" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="83" spans="1:3">
+      <c r="R82">
+        <v>4</v>
+      </c>
+      <c r="T82">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U82">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="83" spans="1:21">
       <c r="A83" t="s">
         <v>99</v>
       </c>
@@ -1877,8 +2623,17 @@
       <c r="C83" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="84" spans="1:3">
+      <c r="R83">
+        <v>4</v>
+      </c>
+      <c r="T83">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U83">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="84" spans="1:21">
       <c r="A84" t="s">
         <v>2</v>
       </c>
@@ -1888,8 +2643,17 @@
       <c r="C84" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="85" spans="1:3">
+      <c r="R84">
+        <v>4</v>
+      </c>
+      <c r="T84">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U84">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="85" spans="1:21">
       <c r="A85" t="s">
         <v>99</v>
       </c>
@@ -1899,8 +2663,17 @@
       <c r="C85" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="86" spans="1:3">
+      <c r="R85">
+        <v>4</v>
+      </c>
+      <c r="T85">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U85">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="86" spans="1:21">
       <c r="A86" t="s">
         <v>2</v>
       </c>
@@ -1910,8 +2683,17 @@
       <c r="C86" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="87" spans="1:3">
+      <c r="R86">
+        <v>4</v>
+      </c>
+      <c r="T86">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U86">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="87" spans="1:21">
       <c r="A87" t="s">
         <v>99</v>
       </c>
@@ -1921,8 +2703,17 @@
       <c r="C87" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="88" spans="1:3">
+      <c r="R87">
+        <v>4</v>
+      </c>
+      <c r="T87">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U87">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="88" spans="1:21">
       <c r="A88" t="s">
         <v>2</v>
       </c>
@@ -1932,8 +2723,17 @@
       <c r="C88" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="89" spans="1:3">
+      <c r="R88">
+        <v>4</v>
+      </c>
+      <c r="T88">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U88">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="89" spans="1:21">
       <c r="A89" t="s">
         <v>99</v>
       </c>
@@ -1943,8 +2743,17 @@
       <c r="C89" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="90" spans="1:3">
+      <c r="R89">
+        <v>4</v>
+      </c>
+      <c r="T89">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U89">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="90" spans="1:21">
       <c r="A90" t="s">
         <v>2</v>
       </c>
@@ -1954,8 +2763,17 @@
       <c r="C90" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="91" spans="1:3">
+      <c r="R90">
+        <v>4</v>
+      </c>
+      <c r="T90">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U90">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="91" spans="1:21">
       <c r="A91" t="s">
         <v>0</v>
       </c>
@@ -1965,8 +2783,17 @@
       <c r="C91" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="92" spans="1:3">
+      <c r="R91">
+        <v>4</v>
+      </c>
+      <c r="T91">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U91">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="92" spans="1:21">
       <c r="A92" t="s">
         <v>99</v>
       </c>
@@ -1976,8 +2803,17 @@
       <c r="C92" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="93" spans="1:3">
+      <c r="R92">
+        <v>4</v>
+      </c>
+      <c r="T92">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U92">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="93" spans="1:21">
       <c r="A93" t="s">
         <v>2</v>
       </c>
@@ -1987,8 +2823,17 @@
       <c r="C93" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="94" spans="1:3">
+      <c r="R93">
+        <v>4</v>
+      </c>
+      <c r="T93">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U93">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="94" spans="1:21">
       <c r="A94" t="s">
         <v>99</v>
       </c>
@@ -1998,8 +2843,17 @@
       <c r="C94" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="95" spans="1:3">
+      <c r="R94">
+        <v>4</v>
+      </c>
+      <c r="T94">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U94">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="95" spans="1:21">
       <c r="A95" t="s">
         <v>0</v>
       </c>
@@ -2009,8 +2863,17 @@
       <c r="C95" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="96" spans="1:3">
+      <c r="R95">
+        <v>4</v>
+      </c>
+      <c r="T95">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U95">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="96" spans="1:21">
       <c r="A96" t="s">
         <v>0</v>
       </c>
@@ -2020,8 +2883,17 @@
       <c r="C96" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="97" spans="1:5">
+      <c r="R96">
+        <v>4</v>
+      </c>
+      <c r="T96">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U96">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="97" spans="1:21">
       <c r="A97" t="s">
         <v>2</v>
       </c>
@@ -2031,8 +2903,17 @@
       <c r="C97" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="98" spans="1:5">
+      <c r="R97">
+        <v>4</v>
+      </c>
+      <c r="T97">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U97">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="98" spans="1:21">
       <c r="A98" t="s">
         <v>99</v>
       </c>
@@ -2042,8 +2923,17 @@
       <c r="C98" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="99" spans="1:5">
+      <c r="R98">
+        <v>4</v>
+      </c>
+      <c r="T98">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U98">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="99" spans="1:21">
       <c r="A99" t="s">
         <v>0</v>
       </c>
@@ -2053,8 +2943,17 @@
       <c r="C99" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="100" spans="1:5">
+      <c r="R99">
+        <v>4</v>
+      </c>
+      <c r="T99">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U99">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="100" spans="1:21">
       <c r="A100" t="s">
         <v>2</v>
       </c>
@@ -2064,8 +2963,17 @@
       <c r="C100" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="1:5">
+      <c r="R100">
+        <v>4</v>
+      </c>
+      <c r="T100">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U100">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="101" spans="1:21">
       <c r="A101" t="s">
         <v>99</v>
       </c>
@@ -2075,8 +2983,17 @@
       <c r="C101" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="102" spans="1:5">
+      <c r="R101">
+        <v>4</v>
+      </c>
+      <c r="T101">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U101">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="102" spans="1:21">
       <c r="A102" t="s">
         <v>2</v>
       </c>
@@ -2086,8 +3003,17 @@
       <c r="C102" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="103" spans="1:5">
+      <c r="R102">
+        <v>4</v>
+      </c>
+      <c r="T102">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U102">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="103" spans="1:21">
       <c r="A103" t="s">
         <v>0</v>
       </c>
@@ -2097,8 +3023,17 @@
       <c r="C103" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="104" spans="1:5">
+      <c r="R103">
+        <v>4</v>
+      </c>
+      <c r="T103">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U103">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="104" spans="1:21">
       <c r="A104" t="s">
         <v>2</v>
       </c>
@@ -2108,8 +3043,17 @@
       <c r="C104" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="105" spans="1:5">
+      <c r="R104">
+        <v>4</v>
+      </c>
+      <c r="T104">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U104">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="105" spans="1:21">
       <c r="A105" t="s">
         <v>99</v>
       </c>
@@ -2119,8 +3063,17 @@
       <c r="C105" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="106" spans="1:5">
+      <c r="R105">
+        <v>4</v>
+      </c>
+      <c r="T105">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U105">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="106" spans="1:21">
       <c r="A106" t="s">
         <v>2</v>
       </c>
@@ -2130,8 +3083,17 @@
       <c r="C106" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="107" spans="1:5">
+      <c r="R106">
+        <v>4</v>
+      </c>
+      <c r="T106">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U106">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="107" spans="1:21">
       <c r="A107" t="s">
         <v>0</v>
       </c>
@@ -2141,8 +3103,17 @@
       <c r="C107" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="108" spans="1:5">
+      <c r="R107">
+        <v>4</v>
+      </c>
+      <c r="T107">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U107">
+        <v>819.16989999999998</v>
+      </c>
+    </row>
+    <row r="108" spans="1:21">
       <c r="A108" t="s">
         <v>132</v>
       </c>
@@ -2157,6 +3128,15 @@
       </c>
       <c r="E108">
         <v>3</v>
+      </c>
+      <c r="R108">
+        <v>4</v>
+      </c>
+      <c r="T108">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U108">
+        <v>819.16989999999998</v>
       </c>
     </row>
   </sheetData>

--- a/TextGame project/Assets/Resources/Story/1.xlsx
+++ b/TextGame project/Assets/Resources/Story/1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Text-Game\TextGame project\Assets\Resources\Story\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{429D00DE-B799-4879-9C80-0B6C9E6ACCF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{379DF9B1-501F-413C-9D2A-C2FA86573E27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -467,14 +467,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>choice1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>choice2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>LastBGImg</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -491,6 +483,14 @@
   </si>
   <si>
     <t>LastX3</t>
+  </si>
+  <si>
+    <t>跟着上去看看</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>还是算了赶紧走吧</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -839,6 +839,7 @@
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="2" max="2" width="66.5546875" customWidth="1"/>
+    <col min="4" max="4" width="20.88671875" customWidth="1"/>
     <col min="7" max="7" width="15.88671875" customWidth="1"/>
     <col min="8" max="8" width="13.6640625" customWidth="1"/>
     <col min="9" max="9" width="15.77734375" customWidth="1"/>
@@ -903,19 +904,19 @@
         <v>37</v>
       </c>
       <c r="R1" t="s">
+        <v>133</v>
+      </c>
+      <c r="S1" t="s">
+        <v>134</v>
+      </c>
+      <c r="T1" t="s">
         <v>135</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
         <v>136</v>
       </c>
-      <c r="T1" t="s">
+      <c r="V1" t="s">
         <v>137</v>
-      </c>
-      <c r="U1" t="s">
-        <v>138</v>
-      </c>
-      <c r="V1" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="2" spans="1:22">
@@ -3118,13 +3119,13 @@
         <v>132</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="C108">
         <v>2</v>
       </c>
       <c r="D108" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E108">
         <v>3</v>

--- a/TextGame project/Assets/Resources/Story/1.xlsx
+++ b/TextGame project/Assets/Resources/Story/1.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Text-Game\TextGame project\Assets\Resources\Story\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\share\Text-Game\TextGame project\Assets\Resources\Story\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{379DF9B1-501F-413C-9D2A-C2FA86573E27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="21942" windowHeight="9805"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,79 +24,140 @@
     <definedName name="OLE_LINK3" localSheetId="0">Sheet1!$B$42</definedName>
     <definedName name="OLE_LINK6" localSheetId="0">Sheet1!$B$55</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="138">
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Dialogue</t>
+  </si>
+  <si>
+    <t>Avatar</t>
+  </si>
+  <si>
+    <t>Vocal</t>
+  </si>
+  <si>
+    <t>BgImg</t>
+  </si>
+  <si>
+    <t>Bgm</t>
+  </si>
+  <si>
+    <t>PageAction</t>
+  </si>
+  <si>
+    <t>PageImage</t>
+  </si>
+  <si>
+    <t>Action1</t>
+  </si>
+  <si>
+    <t>x1</t>
+  </si>
+  <si>
+    <t>Character1</t>
+  </si>
+  <si>
+    <t>Action2</t>
+  </si>
+  <si>
+    <t>x2</t>
+  </si>
+  <si>
+    <t>Character2</t>
+  </si>
+  <si>
+    <t>Action3</t>
+  </si>
+  <si>
+    <t>x3</t>
+  </si>
+  <si>
+    <t>Character3</t>
+  </si>
+  <si>
+    <t>LastBGImg</t>
+  </si>
+  <si>
+    <t>LastBGM</t>
+  </si>
+  <si>
+    <t>LastX1</t>
+  </si>
+  <si>
+    <t>LastX2</t>
+  </si>
+  <si>
+    <t>LastX3</t>
+  </si>
+  <si>
+    <t>appearAt</t>
+  </si>
   <si>
     <t>旁白</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>（千叶坐在书桌前，一边收拾书包一边哼着歌）</t>
   </si>
   <si>
+    <t>White</t>
+  </si>
+  <si>
+    <t>disappear</t>
+  </si>
+  <si>
+    <t>Qianye</t>
+  </si>
+  <si>
     <t>千叶</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>终于到周五了～明天可以好好睡个懒觉！</t>
   </si>
   <si>
-    <t>Qianye</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>（收拾到一半，她拿起手机刷了刷，停了下来）</t>
   </si>
   <si>
     <t>嗯？这是什么...</t>
   </si>
   <si>
-    <t>White</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Name</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dialogue</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Avatar</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Vocal</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BgImg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bgm</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>千叶</t>
-  </si>
-  <si>
-    <t>旁白</t>
+    <t>（手机屏幕上是学校论坛的帖子，标题写着：[你们听说了吗？废弃的临渊高中最近闹鬼了]）</t>
+  </si>
+  <si>
+    <t>临渊高中... 就是郊区那所废弃了好久的学校吗？</t>
   </si>
   <si>
     <t>（她往下翻帖子）</t>
   </si>
   <si>
+    <t>"有人说晚上看到里面有灯光"、"路过的时候听到了奇怪的声音"、"十年前那里有个女生失踪了"...</t>
+  </si>
+  <si>
     <t>（千叶的眼睛亮了起来）</t>
   </si>
   <si>
+    <t>哇，听起来好刺激啊！</t>
+  </si>
+  <si>
     <t>（她站起来，走到窗边，望向远处的方向）</t>
   </si>
   <si>
@@ -110,93 +170,33 @@
     <t>可是... 会不会真的很危险啊？</t>
   </si>
   <si>
+    <t>（她甩了甩头）</t>
+  </si>
+  <si>
     <t>怕什么！不就是个废弃学校嘛，大不了白天去，看一眼就回来。</t>
   </si>
   <si>
-    <t>临渊高中... 就是郊区那所废弃了好久的学校吗？</t>
-  </si>
-  <si>
-    <t>"有人说晚上看到里面有灯光"、"路过的时候听到了奇怪的声音"、"十年前那里有个女生失踪了"...</t>
-  </si>
-  <si>
-    <t>哇，听起来好刺激啊！</t>
-  </si>
-  <si>
-    <t>（她甩了甩头）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>（她把手机塞进口袋，背起书包）</t>
   </si>
   <si>
     <t>好，就这么决定了！明天去探险！</t>
   </si>
   <si>
-    <t>（手机屏幕上是学校论坛的帖子，标题写着：[你们听说了吗？废弃的临渊高中最近闹鬼了]）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Action1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Character1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>x1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Action2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>x2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Character2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Action3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>x3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Character3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>appearAt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>disappear</t>
-  </si>
-  <si>
     <t>（千叶走在上学的路上，一边走一边踢着小石子）</t>
   </si>
   <si>
+    <t>Wangshushu</t>
+  </si>
+  <si>
     <t>（这时，旁边传来一个声音）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>王叔叔</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>千叶，去上学啊？</t>
   </si>
   <si>
-    <t>Wangshushu</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>（千叶转过头，看到隔壁的王叔叔正站在他家门口，笑着看着她）</t>
   </si>
   <si>
@@ -219,7 +219,6 @@
   </si>
   <si>
     <t>（若有所思)这样啊...</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>（他顿了顿，语气变得 "关心" 起来）</t>
@@ -252,41 +251,30 @@
     <t>... 快了，就快了。</t>
   </si>
   <si>
-    <t>（收拾到一半，她拿起手机刷了刷，停了下来）</t>
-  </si>
-  <si>
-    <t>PageAction</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PageImage</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>（周六下午，千叶站在废弃的临渊高中门口）</t>
   </si>
   <si>
     <t>这就是... 临渊高中啊...</t>
   </si>
   <si>
+    <t>（她抬头看着生锈的铁门和斑驳的校名，心里有点发毛）</t>
+  </si>
+  <si>
+    <t>没事没事，大白天的，怕什么！</t>
+  </si>
+  <si>
+    <t>（她推了推铁门，发现有一扇是虚掩着的）</t>
+  </si>
+  <si>
     <t>嗯？这门怎么没锁？</t>
   </si>
   <si>
-    <t>没事没事，大白天的，怕什么！</t>
+    <t>（她探头往里看了看，里面杂草丛生，教学楼的窗户破了好几个）</t>
   </si>
   <si>
     <t>该不会... 真的有人吧？</t>
   </si>
   <si>
-    <t>（她抬头看着生锈的铁门和斑驳的校名，心里有点发毛）</t>
-  </si>
-  <si>
-    <t>（她推了推铁门，发现有一扇是虚掩着的）</t>
-  </si>
-  <si>
-    <t>（她探头往里看了看，里面杂草丛生，教学楼的窗户破了好几个）</t>
-  </si>
-  <si>
     <t>（她咽了口唾沫）</t>
   </si>
   <si>
@@ -353,6 +341,9 @@
     <t>（一个男生的身影从楼梯上走下来，穿着深色的衣服，似乎在找什么东西）</t>
   </si>
   <si>
+    <t>Linshen</t>
+  </si>
+  <si>
     <t>男、男生？他是谁？为什么会在这里？</t>
   </si>
   <si>
@@ -363,16 +354,11 @@
   </si>
   <si>
     <t>林深</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>出来吧。</t>
   </si>
   <si>
-    <t>Linshen</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>（千叶吓了一跳，以为被发现了）</t>
   </si>
   <si>
@@ -464,77 +450,384 @@
   </si>
   <si>
     <t>choice</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LastBGImg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LastBGM</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LastX1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LastX2</t>
-  </si>
-  <si>
-    <t>LastX3</t>
   </si>
   <si>
     <t>跟着上去看看</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>还是算了赶紧走吧</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
+      <sz val="9.8"/>
+      <color rgb="FFC9A26D"/>
+      <name val="JetBrains Mono"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9.8000000000000007"/>
-      <color rgb="FFC9A26D"/>
-      <name val="JetBrains Mono"/>
-      <family val="3"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -542,31 +835,317 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -615,7 +1194,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic Light"/>
@@ -650,7 +1229,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic"/>
@@ -824,104 +1403,99 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:V108"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1"/>
   <cols>
-    <col min="2" max="2" width="66.5546875" customWidth="1"/>
-    <col min="4" max="4" width="20.88671875" customWidth="1"/>
-    <col min="7" max="7" width="15.88671875" customWidth="1"/>
-    <col min="8" max="8" width="13.6640625" customWidth="1"/>
-    <col min="9" max="9" width="15.77734375" customWidth="1"/>
-    <col min="10" max="10" width="13.21875" customWidth="1"/>
-    <col min="11" max="11" width="16.21875" customWidth="1"/>
-    <col min="12" max="12" width="13.33203125" customWidth="1"/>
-    <col min="15" max="15" width="13.6640625" customWidth="1"/>
-    <col min="17" max="17" width="11.77734375" customWidth="1"/>
-    <col min="18" max="18" width="11.5546875" customWidth="1"/>
+    <col min="2" max="2" width="66.5583333333333" customWidth="1"/>
+    <col min="4" max="4" width="20.8833333333333" customWidth="1"/>
+    <col min="7" max="7" width="15.8833333333333" customWidth="1"/>
+    <col min="8" max="8" width="13.6666666666667" customWidth="1"/>
+    <col min="9" max="9" width="15.775" customWidth="1"/>
+    <col min="10" max="10" width="13.2166666666667" customWidth="1"/>
+    <col min="11" max="11" width="16.2166666666667" customWidth="1"/>
+    <col min="12" max="12" width="13.3333333333333" customWidth="1"/>
+    <col min="15" max="15" width="13.6666666666667" customWidth="1"/>
+    <col min="17" max="17" width="11.775" customWidth="1"/>
+    <col min="18" max="18" width="11.5583333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="B1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="C1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="D1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="E1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="F1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="G1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H1" t="s">
-        <v>65</v>
-      </c>
-      <c r="I1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J1" t="s">
-        <v>31</v>
-      </c>
-      <c r="K1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L1" t="s">
-        <v>32</v>
-      </c>
-      <c r="M1" t="s">
-        <v>33</v>
-      </c>
       <c r="N1" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="O1" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="P1" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="Q1" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="R1" t="s">
-        <v>133</v>
+        <v>17</v>
       </c>
       <c r="S1" t="s">
-        <v>134</v>
+        <v>18</v>
       </c>
       <c r="T1" t="s">
-        <v>135</v>
+        <v>19</v>
       </c>
       <c r="U1" t="s">
-        <v>136</v>
+        <v>20</v>
       </c>
       <c r="V1" t="s">
-        <v>137</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:22">
-      <c r="G2" s="2" t="s">
-        <v>38</v>
+      <c r="G2" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -929,2203 +1503,2203 @@
     </row>
     <row r="3" spans="1:22">
       <c r="A3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>23</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>38</v>
+      <c r="G3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="J3">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="K3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:22">
       <c r="A4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>1</v>
+        <v>23</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K4" s="2"/>
+        <v>25</v>
+      </c>
+      <c r="K4" s="1"/>
       <c r="R4">
         <v>1</v>
       </c>
       <c r="T4">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U4">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="5" spans="1:22">
       <c r="A5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>3</v>
+        <v>28</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="R5">
         <v>1</v>
       </c>
       <c r="T5">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U5">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>63</v>
+        <v>23</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="R6">
         <v>1</v>
       </c>
       <c r="T6">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U6">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="7" spans="1:22">
       <c r="A7" t="s">
-        <v>2</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>5</v>
+        <v>28</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="R7">
         <v>1</v>
       </c>
       <c r="T7">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U7">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="C8" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="R8">
         <v>1</v>
       </c>
       <c r="T8">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U8">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="9" spans="1:22">
       <c r="A9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="R9">
         <v>1</v>
       </c>
       <c r="T9">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U9">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="C10" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="R10">
         <v>1</v>
       </c>
       <c r="T10">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U10">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="C11" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="R11">
         <v>1</v>
       </c>
       <c r="T11">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U11">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="C12" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="R12">
         <v>1</v>
       </c>
       <c r="T12">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U12">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="C13" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="R13">
         <v>1</v>
       </c>
       <c r="T13">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U13">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="C14" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="R14">
         <v>1</v>
       </c>
       <c r="T14">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U14">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>18</v>
+        <v>28</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="C15" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="R15">
         <v>1</v>
       </c>
       <c r="T15">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U15">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>40</v>
       </c>
       <c r="C16" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="R16">
         <v>1</v>
       </c>
       <c r="T16">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U16">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="17" spans="1:21">
       <c r="A17" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>20</v>
+        <v>28</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="C17" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="R17">
         <v>1</v>
       </c>
       <c r="T17">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U17">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="18" spans="1:21">
       <c r="A18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="C18" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="R18">
         <v>1</v>
       </c>
       <c r="T18">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U18">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="19" spans="1:21">
       <c r="A19" t="s">
-        <v>13</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="C19" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="R19">
         <v>1</v>
       </c>
       <c r="T19">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U19">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="20" spans="1:21">
       <c r="A20" t="s">
-        <v>14</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="C20" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="R20">
         <v>1</v>
       </c>
       <c r="T20">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U20">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="21" spans="1:21">
       <c r="A21" t="s">
-        <v>13</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="C21" t="s">
-        <v>4</v>
-      </c>
-      <c r="I21" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="I21" s="1"/>
       <c r="R21">
         <v>1</v>
       </c>
       <c r="T21">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U21">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="22" spans="1:21">
       <c r="A22" t="s">
-        <v>14</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>40</v>
+        <v>23</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="C22" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="E22">
         <v>2</v>
       </c>
-      <c r="I22" s="2"/>
-      <c r="L22" s="2" t="s">
-        <v>38</v>
+      <c r="I22" s="1"/>
+      <c r="L22" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="M22">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
       <c r="N22" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="R22">
         <v>1</v>
       </c>
       <c r="T22">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U22">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="23" spans="1:21">
       <c r="A23" t="s">
-        <v>14</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>41</v>
+        <v>23</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="C23" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="R23">
         <v>2</v>
       </c>
       <c r="T23">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U23">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="24" spans="1:21">
       <c r="A24" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C24" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="R24">
         <v>2</v>
       </c>
       <c r="T24">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U24">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="25" spans="1:21">
       <c r="A25" t="s">
-        <v>14</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>45</v>
+        <v>23</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>51</v>
       </c>
       <c r="C25" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="R25">
         <v>2</v>
       </c>
       <c r="T25">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U25">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="26" spans="1:21">
       <c r="A26" t="s">
-        <v>13</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>46</v>
+        <v>28</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>52</v>
       </c>
       <c r="C26" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="R26">
         <v>2</v>
       </c>
       <c r="T26">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U26">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="27" spans="1:21">
       <c r="A27" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C27" t="s">
         <v>47</v>
-      </c>
-      <c r="C27" t="s">
-        <v>44</v>
       </c>
       <c r="R27">
         <v>2</v>
       </c>
       <c r="T27">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U27">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="28" spans="1:21">
       <c r="A28" t="s">
-        <v>13</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>48</v>
+        <v>28</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="C28" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="R28">
         <v>2</v>
       </c>
       <c r="T28">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U28">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="29" spans="1:21">
       <c r="A29" t="s">
-        <v>42</v>
-      </c>
-      <c r="B29" s="1" t="s">
         <v>49</v>
       </c>
+      <c r="B29" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="C29" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="R29">
         <v>2</v>
       </c>
       <c r="T29">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U29">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="30" spans="1:21">
       <c r="A30" t="s">
-        <v>13</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>50</v>
+        <v>28</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="C30" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="R30">
         <v>2</v>
       </c>
       <c r="T30">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U30">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="31" spans="1:21">
       <c r="A31" t="s">
-        <v>14</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>51</v>
+        <v>23</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>57</v>
       </c>
       <c r="C31" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="R31">
         <v>2</v>
       </c>
       <c r="T31">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U31">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="32" spans="1:21">
       <c r="A32" t="s">
-        <v>42</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>58</v>
       </c>
       <c r="C32" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="R32">
         <v>2</v>
       </c>
       <c r="T32">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U32">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="33" spans="1:21">
       <c r="A33" t="s">
-        <v>14</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>53</v>
+        <v>23</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>59</v>
       </c>
       <c r="C33" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="R33">
         <v>2</v>
       </c>
       <c r="T33">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U33">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="34" spans="1:21">
       <c r="A34" t="s">
-        <v>42</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>54</v>
+        <v>49</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>60</v>
       </c>
       <c r="C34" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="R34">
         <v>2</v>
       </c>
       <c r="T34">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U34">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="35" spans="1:21">
       <c r="A35" t="s">
-        <v>13</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>55</v>
+        <v>28</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="C35" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="R35">
         <v>2</v>
       </c>
       <c r="T35">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U35">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="36" spans="1:21">
       <c r="A36" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="C36" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="R36">
         <v>2</v>
       </c>
       <c r="T36">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U36">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="37" spans="1:21">
       <c r="A37" t="s">
-        <v>13</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>57</v>
+        <v>28</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="C37" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="R37">
         <v>2</v>
       </c>
       <c r="T37">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U37">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="38" spans="1:21">
       <c r="A38" t="s">
-        <v>42</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>58</v>
+        <v>49</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="C38" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="R38">
         <v>2</v>
       </c>
       <c r="T38">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U38">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="39" spans="1:21">
       <c r="A39" t="s">
-        <v>13</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>59</v>
+        <v>28</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="C39" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="R39">
         <v>2</v>
       </c>
       <c r="T39">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U39">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="40" spans="1:21">
       <c r="A40" t="s">
-        <v>14</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>60</v>
+        <v>23</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="C40" t="s">
-        <v>6</v>
-      </c>
-      <c r="I40" s="2" t="s">
-        <v>39</v>
+        <v>25</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="R40">
         <v>2</v>
       </c>
       <c r="T40">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U40">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="41" spans="1:21">
       <c r="A41" t="s">
-        <v>14</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>61</v>
+        <v>23</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="C41" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="R41">
         <v>2</v>
       </c>
       <c r="T41">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U41">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="42" spans="1:21">
       <c r="A42" t="s">
-        <v>42</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>62</v>
+        <v>49</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>68</v>
       </c>
       <c r="C42" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="R42">
         <v>2</v>
       </c>
       <c r="T42">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U42">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="43" spans="1:21">
       <c r="A43" t="s">
-        <v>42</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>62</v>
+        <v>49</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>68</v>
       </c>
       <c r="C43" t="s">
-        <v>44</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>38</v>
+        <v>47</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="H43">
         <v>1</v>
       </c>
-      <c r="L43" s="2" t="s">
-        <v>39</v>
+      <c r="L43" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="R43">
         <v>2</v>
       </c>
       <c r="T43">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U43">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="44" spans="1:21">
       <c r="A44" t="s">
-        <v>14</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>66</v>
+        <v>23</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>69</v>
       </c>
       <c r="C44" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="E44">
         <v>3</v>
       </c>
-      <c r="G44" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="I44" s="2" t="s">
-        <v>38</v>
+      <c r="G44" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="J44">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="K44" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="R44">
         <v>2</v>
       </c>
       <c r="T44">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U44">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="45" spans="1:21">
       <c r="A45" t="s">
-        <v>13</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>67</v>
+        <v>28</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>70</v>
       </c>
       <c r="C45" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="R45">
         <v>3</v>
       </c>
       <c r="T45">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U45">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="46" spans="1:21">
       <c r="A46" t="s">
-        <v>14</v>
-      </c>
-      <c r="B46" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B46" s="2" t="s">
         <v>71</v>
       </c>
       <c r="C46" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="R46">
         <v>3</v>
       </c>
       <c r="T46">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U46">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="47" spans="1:21">
       <c r="A47" t="s">
-        <v>13</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>69</v>
+        <v>28</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>72</v>
       </c>
       <c r="C47" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="R47">
         <v>3</v>
       </c>
       <c r="T47">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U47">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="48" spans="1:21">
       <c r="A48" t="s">
-        <v>14</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>72</v>
+        <v>23</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>73</v>
       </c>
       <c r="C48" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="R48">
         <v>3</v>
       </c>
       <c r="T48">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U48">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="49" spans="1:21">
       <c r="A49" t="s">
-        <v>13</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>68</v>
+        <v>28</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>74</v>
       </c>
       <c r="C49" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="R49">
         <v>3</v>
       </c>
       <c r="T49">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U49">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="50" spans="1:21">
       <c r="A50" t="s">
-        <v>14</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>73</v>
+        <v>23</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>75</v>
       </c>
       <c r="C50" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="R50">
         <v>3</v>
       </c>
       <c r="T50">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U50">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="51" spans="1:21">
       <c r="A51" t="s">
-        <v>2</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>70</v>
+        <v>28</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>76</v>
       </c>
       <c r="C51" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="R51">
         <v>3</v>
       </c>
       <c r="T51">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U51">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="52" spans="1:21">
       <c r="A52" t="s">
-        <v>14</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>74</v>
+        <v>23</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>77</v>
       </c>
       <c r="C52" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="R52">
         <v>3</v>
       </c>
       <c r="T52">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U52">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="53" spans="1:21">
       <c r="A53" t="s">
-        <v>2</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>75</v>
+        <v>28</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="C53" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="R53">
         <v>3</v>
       </c>
       <c r="T53">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U53">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="54" spans="1:21">
       <c r="A54" t="s">
-        <v>0</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>76</v>
+        <v>23</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>79</v>
       </c>
       <c r="C54" t="s">
-        <v>6</v>
-      </c>
-      <c r="I54" s="2" t="s">
-        <v>39</v>
+        <v>25</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="R54">
         <v>3</v>
       </c>
       <c r="T54">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U54">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="55" spans="1:21">
       <c r="A55" t="s">
-        <v>0</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>77</v>
+        <v>23</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>80</v>
       </c>
       <c r="C55" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="E55">
         <v>4</v>
       </c>
-      <c r="I55" s="2" t="s">
-        <v>38</v>
+      <c r="I55" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="J55">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="K55" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="R55">
         <v>3</v>
       </c>
       <c r="T55">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U55">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="56" spans="1:21">
       <c r="A56" t="s">
-        <v>2</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>78</v>
+        <v>28</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>81</v>
       </c>
       <c r="C56" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="R56">
         <v>4</v>
       </c>
       <c r="T56">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U56">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="57" spans="1:21">
       <c r="A57" t="s">
-        <v>0</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>79</v>
+        <v>23</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>82</v>
       </c>
       <c r="C57" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="R57">
         <v>4</v>
       </c>
       <c r="T57">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U57">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="58" spans="1:21">
       <c r="A58" t="s">
-        <v>0</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>80</v>
+        <v>23</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>83</v>
       </c>
       <c r="C58" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="R58">
         <v>4</v>
       </c>
       <c r="T58">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U58">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="59" spans="1:21">
       <c r="A59" t="s">
-        <v>2</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>81</v>
+        <v>28</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>84</v>
       </c>
       <c r="C59" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="R59">
         <v>4</v>
       </c>
       <c r="T59">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U59">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="60" spans="1:21">
       <c r="A60" t="s">
-        <v>0</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>82</v>
+        <v>23</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="C60" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="R60">
         <v>4</v>
       </c>
       <c r="T60">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U60">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="61" spans="1:21">
       <c r="A61" t="s">
-        <v>2</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>83</v>
+        <v>28</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>86</v>
       </c>
       <c r="C61" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="R61">
         <v>4</v>
       </c>
       <c r="T61">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U61">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="62" spans="1:21">
       <c r="A62" t="s">
-        <v>0</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>84</v>
+        <v>23</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>87</v>
       </c>
       <c r="C62" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="R62">
         <v>4</v>
       </c>
       <c r="T62">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U62">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="63" spans="1:21">
       <c r="A63" t="s">
-        <v>0</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>85</v>
+        <v>23</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="C63" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="R63">
         <v>4</v>
       </c>
       <c r="T63">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U63">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="64" spans="1:21">
       <c r="A64" t="s">
-        <v>2</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>86</v>
+        <v>28</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="C64" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="R64">
         <v>4</v>
       </c>
       <c r="T64">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U64">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="65" spans="1:21">
       <c r="A65" t="s">
-        <v>0</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>87</v>
+        <v>23</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>90</v>
       </c>
       <c r="C65" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="R65">
         <v>4</v>
       </c>
       <c r="T65">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U65">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="66" spans="1:21">
       <c r="A66" t="s">
-        <v>0</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>88</v>
+        <v>23</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>91</v>
       </c>
       <c r="C66" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="R66">
         <v>4</v>
       </c>
       <c r="T66">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U66">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="67" spans="1:21">
       <c r="A67" t="s">
-        <v>2</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>89</v>
+        <v>28</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>92</v>
       </c>
       <c r="C67" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="R67">
         <v>4</v>
       </c>
       <c r="T67">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U67">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="68" spans="1:21">
       <c r="A68" t="s">
-        <v>0</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>90</v>
+        <v>23</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="C68" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="R68">
         <v>4</v>
       </c>
       <c r="T68">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U68">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="69" spans="1:21">
       <c r="A69" t="s">
-        <v>0</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>91</v>
+        <v>23</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>94</v>
       </c>
       <c r="C69" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="R69">
         <v>4</v>
       </c>
       <c r="T69">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U69">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="70" spans="1:21">
       <c r="A70" t="s">
-        <v>2</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>92</v>
+        <v>28</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>95</v>
       </c>
       <c r="C70" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="R70">
         <v>4</v>
       </c>
       <c r="T70">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U70">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="71" spans="1:21">
       <c r="A71" t="s">
-        <v>0</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>93</v>
+        <v>23</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>96</v>
       </c>
       <c r="C71" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="R71">
         <v>4</v>
       </c>
       <c r="T71">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U71">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="72" spans="1:21">
       <c r="A72" t="s">
-        <v>0</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>94</v>
+        <v>23</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="C72" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="R72">
         <v>4</v>
       </c>
       <c r="T72">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U72">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="73" spans="1:21">
       <c r="A73" t="s">
-        <v>0</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>95</v>
+        <v>23</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>98</v>
       </c>
       <c r="C73" t="s">
-        <v>6</v>
-      </c>
-      <c r="L73" s="2" t="s">
-        <v>38</v>
+        <v>25</v>
+      </c>
+      <c r="L73" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="M73">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
       <c r="N73" t="s">
-        <v>101</v>
-      </c>
-      <c r="O73" s="2"/>
+        <v>99</v>
+      </c>
+      <c r="O73" s="1"/>
       <c r="R73">
         <v>4</v>
       </c>
       <c r="T73">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U73">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="74" spans="1:21">
       <c r="A74" t="s">
-        <v>2</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>96</v>
+        <v>28</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>100</v>
       </c>
       <c r="C74" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="R74">
         <v>4</v>
       </c>
       <c r="T74">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U74">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="75" spans="1:21">
       <c r="A75" t="s">
-        <v>0</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>97</v>
+        <v>23</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="C75" t="s">
-        <v>6</v>
-      </c>
-      <c r="I75" s="2" t="s">
-        <v>39</v>
+        <v>25</v>
+      </c>
+      <c r="I75" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="R75">
         <v>4</v>
       </c>
       <c r="T75">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U75">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="76" spans="1:21">
       <c r="A76" t="s">
-        <v>0</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>98</v>
+        <v>23</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>102</v>
       </c>
       <c r="C76" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="R76">
         <v>4</v>
       </c>
       <c r="T76">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U76">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="77" spans="1:21">
       <c r="A77" t="s">
+        <v>103</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C77" t="s">
         <v>99</v>
       </c>
-      <c r="B77" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C77" t="s">
-        <v>101</v>
-      </c>
       <c r="R77">
         <v>4</v>
       </c>
       <c r="T77">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U77">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="78" spans="1:21">
       <c r="A78" t="s">
-        <v>0</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>102</v>
+        <v>23</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>105</v>
       </c>
       <c r="C78" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="R78">
         <v>4</v>
       </c>
       <c r="T78">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U78">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="79" spans="1:21">
       <c r="A79" t="s">
+        <v>103</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C79" t="s">
         <v>99</v>
       </c>
-      <c r="B79" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C79" t="s">
-        <v>101</v>
-      </c>
       <c r="R79">
         <v>4</v>
       </c>
       <c r="T79">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U79">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="80" spans="1:21">
       <c r="A80" t="s">
-        <v>0</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>104</v>
+        <v>23</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>107</v>
       </c>
       <c r="C80" t="s">
-        <v>6</v>
-      </c>
-      <c r="I80" s="2" t="s">
-        <v>38</v>
+        <v>25</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="J80">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="K80" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="R80">
         <v>4</v>
       </c>
       <c r="T80">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U80">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="81" spans="1:21">
       <c r="A81" t="s">
-        <v>0</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>105</v>
+        <v>23</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>108</v>
       </c>
       <c r="C81" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="R81">
         <v>4</v>
       </c>
       <c r="T81">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U81">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="82" spans="1:21">
       <c r="A82" t="s">
-        <v>2</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>106</v>
+        <v>28</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="C82" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="R82">
         <v>4</v>
       </c>
       <c r="T82">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U82">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="83" spans="1:21">
       <c r="A83" t="s">
+        <v>103</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C83" t="s">
         <v>99</v>
       </c>
-      <c r="B83" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C83" t="s">
-        <v>101</v>
-      </c>
       <c r="R83">
         <v>4</v>
       </c>
       <c r="T83">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U83">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="84" spans="1:21">
       <c r="A84" t="s">
-        <v>2</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>108</v>
+        <v>28</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>111</v>
       </c>
       <c r="C84" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="R84">
         <v>4</v>
       </c>
       <c r="T84">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U84">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="85" spans="1:21">
       <c r="A85" t="s">
+        <v>103</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C85" t="s">
         <v>99</v>
       </c>
-      <c r="B85" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C85" t="s">
-        <v>101</v>
-      </c>
       <c r="R85">
         <v>4</v>
       </c>
       <c r="T85">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U85">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="86" spans="1:21">
       <c r="A86" t="s">
-        <v>2</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>110</v>
+        <v>28</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>113</v>
       </c>
       <c r="C86" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="R86">
         <v>4</v>
       </c>
       <c r="T86">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U86">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="87" spans="1:21">
       <c r="A87" t="s">
+        <v>103</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C87" t="s">
         <v>99</v>
       </c>
-      <c r="B87" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C87" t="s">
-        <v>101</v>
-      </c>
       <c r="R87">
         <v>4</v>
       </c>
       <c r="T87">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U87">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="88" spans="1:21">
       <c r="A88" t="s">
-        <v>2</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>112</v>
+        <v>28</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>115</v>
       </c>
       <c r="C88" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="R88">
         <v>4</v>
       </c>
       <c r="T88">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U88">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="89" spans="1:21">
       <c r="A89" t="s">
+        <v>103</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C89" t="s">
         <v>99</v>
       </c>
-      <c r="B89" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C89" t="s">
-        <v>101</v>
-      </c>
       <c r="R89">
         <v>4</v>
       </c>
       <c r="T89">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U89">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="90" spans="1:21">
       <c r="A90" t="s">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C90" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="R90">
         <v>4</v>
       </c>
       <c r="T90">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U90">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="91" spans="1:21">
       <c r="A91" t="s">
-        <v>0</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>115</v>
+        <v>23</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>118</v>
       </c>
       <c r="C91" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="R91">
         <v>4</v>
       </c>
       <c r="T91">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U91">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="92" spans="1:21">
       <c r="A92" t="s">
+        <v>103</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C92" t="s">
         <v>99</v>
       </c>
-      <c r="B92" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C92" t="s">
-        <v>101</v>
-      </c>
       <c r="R92">
         <v>4</v>
       </c>
       <c r="T92">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U92">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="93" spans="1:21">
       <c r="A93" t="s">
-        <v>2</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>117</v>
+        <v>28</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>120</v>
       </c>
       <c r="C93" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="R93">
         <v>4</v>
       </c>
       <c r="T93">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U93">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="94" spans="1:21">
       <c r="A94" t="s">
+        <v>103</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C94" t="s">
         <v>99</v>
       </c>
-      <c r="B94" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="C94" t="s">
-        <v>101</v>
-      </c>
       <c r="R94">
         <v>4</v>
       </c>
       <c r="T94">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U94">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="95" spans="1:21">
       <c r="A95" t="s">
-        <v>0</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>119</v>
+        <v>23</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>122</v>
       </c>
       <c r="C95" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="R95">
         <v>4</v>
       </c>
       <c r="T95">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U95">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="96" spans="1:21">
       <c r="A96" t="s">
-        <v>0</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>120</v>
+        <v>23</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>123</v>
       </c>
       <c r="C96" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="R96">
         <v>4</v>
       </c>
       <c r="T96">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U96">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="97" spans="1:21">
       <c r="A97" t="s">
-        <v>2</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>121</v>
+        <v>28</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>124</v>
       </c>
       <c r="C97" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="R97">
         <v>4</v>
       </c>
       <c r="T97">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U97">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="98" spans="1:21">
       <c r="A98" t="s">
+        <v>103</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C98" t="s">
         <v>99</v>
       </c>
-      <c r="B98" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C98" t="s">
-        <v>101</v>
-      </c>
       <c r="R98">
         <v>4</v>
       </c>
       <c r="T98">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U98">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="99" spans="1:21">
       <c r="A99" t="s">
-        <v>0</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>123</v>
+        <v>23</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>126</v>
       </c>
       <c r="C99" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="R99">
         <v>4</v>
       </c>
       <c r="T99">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U99">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="100" spans="1:21">
       <c r="A100" t="s">
-        <v>2</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>124</v>
+        <v>28</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>127</v>
       </c>
       <c r="C100" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="R100">
         <v>4</v>
       </c>
       <c r="T100">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U100">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="101" spans="1:21">
       <c r="A101" t="s">
+        <v>103</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C101" t="s">
         <v>99</v>
       </c>
-      <c r="B101" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="C101" t="s">
-        <v>101</v>
-      </c>
       <c r="R101">
         <v>4</v>
       </c>
       <c r="T101">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U101">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="102" spans="1:21">
       <c r="A102" t="s">
-        <v>2</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>126</v>
+        <v>28</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>129</v>
       </c>
       <c r="C102" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="R102">
         <v>4</v>
       </c>
       <c r="T102">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U102">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="103" spans="1:21">
       <c r="A103" t="s">
-        <v>0</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>127</v>
+        <v>23</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>130</v>
       </c>
       <c r="C103" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="R103">
         <v>4</v>
       </c>
       <c r="T103">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U103">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="104" spans="1:21">
       <c r="A104" t="s">
-        <v>2</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>128</v>
+        <v>28</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>131</v>
       </c>
       <c r="C104" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="R104">
         <v>4</v>
       </c>
       <c r="T104">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U104">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="105" spans="1:21">
       <c r="A105" t="s">
+        <v>103</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C105" t="s">
         <v>99</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="C105" t="s">
-        <v>101</v>
-      </c>
       <c r="R105">
         <v>4</v>
       </c>
       <c r="T105">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U105">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="106" spans="1:21">
       <c r="A106" t="s">
-        <v>2</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>130</v>
+        <v>28</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>133</v>
       </c>
       <c r="C106" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="R106">
         <v>4</v>
       </c>
       <c r="T106">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U106">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="107" spans="1:21">
       <c r="A107" t="s">
-        <v>0</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>131</v>
+        <v>23</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>134</v>
       </c>
       <c r="C107" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="R107">
         <v>4</v>
       </c>
       <c r="T107">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U107">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
     <row r="108" spans="1:21">
       <c r="A108" t="s">
-        <v>132</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>136</v>
       </c>
       <c r="C108">
         <v>2</v>
       </c>
       <c r="D108" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E108">
         <v>3</v>
@@ -3134,15 +3708,15 @@
         <v>4</v>
       </c>
       <c r="T108">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="U108">
-        <v>819.16989999999998</v>
+        <v>819.1699</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/TextGame project/Assets/Resources/Story/1.xlsx
+++ b/TextGame project/Assets/Resources/Story/1.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\share\Text-Game\TextGame project\Assets\Resources\Story\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Text-Game\TextGame project\Assets\Resources\Story\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33EFFFD3-FE20-4F23-A505-56E4B60AA68D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="21942" windowHeight="9805"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -137,27 +138,15 @@
     <t>（收拾到一半，她拿起手机刷了刷，停了下来）</t>
   </si>
   <si>
-    <t>嗯？这是什么...</t>
-  </si>
-  <si>
     <t>（手机屏幕上是学校论坛的帖子，标题写着：[你们听说了吗？废弃的临渊高中最近闹鬼了]）</t>
   </si>
   <si>
-    <t>临渊高中... 就是郊区那所废弃了好久的学校吗？</t>
-  </si>
-  <si>
     <t>（她往下翻帖子）</t>
   </si>
   <si>
-    <t>"有人说晚上看到里面有灯光"、"路过的时候听到了奇怪的声音"、"十年前那里有个女生失踪了"...</t>
-  </si>
-  <si>
     <t>（千叶的眼睛亮了起来）</t>
   </si>
   <si>
-    <t>哇，听起来好刺激啊！</t>
-  </si>
-  <si>
     <t>（她站起来，走到窗边，望向远处的方向）</t>
   </si>
   <si>
@@ -167,15 +156,9 @@
     <t>（她想了想，又有点犹豫）</t>
   </si>
   <si>
-    <t>可是... 会不会真的很危险啊？</t>
-  </si>
-  <si>
     <t>（她甩了甩头）</t>
   </si>
   <si>
-    <t>怕什么！不就是个废弃学校嘛，大不了白天去，看一眼就回来。</t>
-  </si>
-  <si>
     <t>（她把手机塞进口袋，背起书包）</t>
   </si>
   <si>
@@ -194,27 +177,12 @@
     <t>王叔叔</t>
   </si>
   <si>
-    <t>千叶，去上学啊？</t>
-  </si>
-  <si>
     <t>（千叶转过头，看到隔壁的王叔叔正站在他家门口，笑着看着她）</t>
   </si>
   <si>
-    <t>王叔叔早！</t>
-  </si>
-  <si>
-    <t>早啊。看你今天心情不错，有什么开心的事吗？</t>
-  </si>
-  <si>
     <t>没什么啦，就是想到周末了，有点开心。</t>
   </si>
   <si>
-    <t>哈哈，年轻人就是好啊。周末有什么打算吗？</t>
-  </si>
-  <si>
-    <t>嗯... 还没想好呢，可能在家写作业吧。</t>
-  </si>
-  <si>
     <t>（她没说要去废弃学校的事，觉得说了可能会被骂）</t>
   </si>
   <si>
@@ -224,114 +192,60 @@
     <t>（他顿了顿，语气变得 "关心" 起来）</t>
   </si>
   <si>
-    <t>千叶啊，王叔叔提醒你一句，最近别往偏僻的地方跑，尤其是郊区那边，不太安全。</t>
-  </si>
-  <si>
-    <t>啊？为什么啊？</t>
-  </si>
-  <si>
-    <t>最近附近不太太平，你一个女孩子，要注意安全。知道吗？</t>
-  </si>
-  <si>
-    <t>哦... 知道了，谢谢王叔叔。</t>
-  </si>
-  <si>
-    <t>嗯，乖。快去吧，别迟到了。</t>
-  </si>
-  <si>
-    <t>王叔叔再见！</t>
-  </si>
-  <si>
     <t>（千叶跑走了）</t>
   </si>
   <si>
     <t>（王叔叔站在原地，看着千叶的背影，脸上的笑容慢慢消失了，眼神变得阴冷）</t>
   </si>
   <si>
-    <t>... 快了，就快了。</t>
-  </si>
-  <si>
     <t>（周六下午，千叶站在废弃的临渊高中门口）</t>
   </si>
   <si>
-    <t>这就是... 临渊高中啊...</t>
-  </si>
-  <si>
     <t>（她抬头看着生锈的铁门和斑驳的校名，心里有点发毛）</t>
   </si>
   <si>
-    <t>没事没事，大白天的，怕什么！</t>
-  </si>
-  <si>
     <t>（她推了推铁门，发现有一扇是虚掩着的）</t>
   </si>
   <si>
-    <t>嗯？这门怎么没锁？</t>
-  </si>
-  <si>
     <t>（她探头往里看了看，里面杂草丛生，教学楼的窗户破了好几个）</t>
   </si>
   <si>
-    <t>该不会... 真的有人吧？</t>
-  </si>
-  <si>
     <t>（她咽了口唾沫）</t>
   </si>
   <si>
-    <t>来都来了，进去看看！</t>
-  </si>
-  <si>
     <t>（她深吸一口气，推开铁门走了进去）</t>
   </si>
   <si>
     <t>（千叶走在空荡荡的走廊里，脚步声回响着）</t>
   </si>
   <si>
-    <t>好安静啊...</t>
-  </si>
-  <si>
     <t>（走廊两边的教室门都破破烂烂的，有的半开着，里面黑漆漆的）</t>
   </si>
   <si>
     <t>（她往一间教室里看了一眼，里面的课桌椅东倒西歪，黑板上还有模糊的字迹）</t>
   </si>
   <si>
-    <t>感觉... 好荒凉啊。</t>
-  </si>
-  <si>
     <t>（她继续往前走，越走越觉得不对劲）</t>
   </si>
   <si>
-    <t>奇怪，怎么感觉... 好像有别的声音？</t>
-  </si>
-  <si>
     <t>（她停下来，仔细听）</t>
   </si>
   <si>
     <t>（除了自己的心跳声，好像还有... 别的脚步声？）</t>
   </si>
   <si>
-    <t>不、不会吧...</t>
-  </si>
-  <si>
     <t>（她开始害怕了，想着要不要回去）</t>
   </si>
   <si>
     <t>（但好奇心又占了上风）</t>
   </si>
   <si>
-    <t>就、就再往前走一点，看看就走。</t>
-  </si>
-  <si>
     <t>（她蹑手蹑脚地继续往前走）</t>
   </si>
   <si>
     <t>（走到楼梯口的时候，她听到楼上传来什么东西倒地的声音）</t>
   </si>
   <si>
-    <t>！！</t>
-  </si>
-  <si>
     <t>（她赶紧躲到墙角，心脏砰砰直跳）</t>
   </si>
   <si>
@@ -344,9 +258,6 @@
     <t>Linshen</t>
   </si>
   <si>
-    <t>男、男生？他是谁？为什么会在这里？</t>
-  </si>
-  <si>
     <t>（她紧张地看着那个男生）</t>
   </si>
   <si>
@@ -356,96 +267,30 @@
     <t>林深</t>
   </si>
   <si>
-    <t>出来吧。</t>
-  </si>
-  <si>
     <t>（千叶吓了一跳，以为被发现了）</t>
   </si>
   <si>
-    <t>躲在那里有意思吗？</t>
-  </si>
-  <si>
     <t>（千叶知道躲不过去了，只好硬着头皮走了出来）</t>
   </si>
   <si>
     <t>（千叶从墙角走出来，和林深面对面站着）</t>
   </si>
   <si>
-    <t>你、你是谁啊？为什么会在这里？</t>
-  </si>
-  <si>
-    <t>这句话应该我问你。</t>
-  </si>
-  <si>
-    <t>我... 我是来探险的！</t>
-  </si>
-  <si>
-    <t>探险？</t>
-  </si>
-  <si>
-    <t>对！听说这里闹鬼，我来看看是不是真的。</t>
-  </si>
-  <si>
-    <t>无聊。</t>
-  </si>
-  <si>
-    <t>喂！你什么意思啊！</t>
-  </si>
-  <si>
-    <t>这里不是你该来的地方，赶紧走。</t>
-  </si>
-  <si>
-    <t>你凭什么管我啊！你又是谁？为什么会在这里？</t>
-  </si>
-  <si>
     <t>（林深停下脚步，背对着她）</t>
   </si>
   <si>
-    <t>我来调查一些事情。</t>
-  </si>
-  <si>
-    <t>调查？调查什么？</t>
-  </si>
-  <si>
-    <t>和你无关。</t>
-  </si>
-  <si>
     <t>（就在这时，楼上传来一声巨响，像是有什么东西倒了）</t>
   </si>
   <si>
     <t>（两人同时安静下来，看向楼上）</t>
   </si>
   <si>
-    <t>那、那是什么声音？</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ...</t>
-  </si>
-  <si>
     <t>（他看向楼上，似乎在思考什么）</t>
   </si>
   <si>
-    <t>该不会... 真的有鬼吧？</t>
-  </si>
-  <si>
-    <t>世界上没有鬼。</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 那你说是什么...</t>
-  </si>
-  <si>
     <t>（林深没回答，转身往楼梯的方向走）</t>
   </si>
   <si>
-    <t>喂！你去哪儿？</t>
-  </si>
-  <si>
-    <t>上去看看。</t>
-  </si>
-  <si>
-    <t>等、等一下啊！</t>
-  </si>
-  <si>
     <t>（她站在原地，不知道该怎么办）</t>
   </si>
   <si>
@@ -456,19 +301,221 @@
   </si>
   <si>
     <t>还是算了赶紧走吧</t>
+  </si>
+  <si>
+    <t>（疑惑）嗯？这是什么...</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（好奇）临渊高中... 就是郊区那所废弃了好久的学校吗？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（自言自语）"有人说晚上看到里面有灯光"、"路过的时候听到了奇怪的声音"、"十年前那里有个女生失踪了"...</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（兴奋）哇，听起来好刺激啊！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（纠结）可是... 会不会真的很危险啊？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（坚定）怕什么！不就是个废弃学校嘛，大不了白天去，看一眼就回来。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（画外音，温和）千叶，去上学啊？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（微笑）王叔叔早！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（温和）早啊。看你今天心情不错，有什么开心的事吗？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（微笑）哈哈，年轻人就是好啊。周末有什么打算吗？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（犹豫了一下）嗯... 还没想好呢，可能在家写作业吧。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（认真）千叶啊，王叔叔提醒你一句，最近别往偏僻的地方跑，尤其是郊区那边，不太安全。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（疑惑）啊？为什么啊？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（严肃）最近附近不太太平，你一个女孩子，要注意安全。知道吗？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（点头）哦... 知道了，谢谢王叔叔。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（微笑）嗯，乖。快去吧，别迟到了。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（挥手）王叔叔再见！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（低语，画外音）... 快了，就快了。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（紧张）这就是... 临渊高中啊...</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（给自己打气）没事没事，大白天的，怕什么！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（疑惑）嗯？这门怎么没锁？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（犹豫）该不会... 真的有人吧？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（坚定）来都来了，进去看看！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（小声嘀咕）好安静啊...</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（感慨）感觉... 好荒凉啊。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（疑惑）奇怪，怎么感觉... 好像有别的声音？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（紧张）不、不会吧...</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（小声）就、就再往前走一点，看看就走。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（惊吓）！！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（内心）男、男生？他是谁？为什么会在这里？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（冷淡，画外音）出来吧。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（冷淡）躲在那里有意思吗？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（紧张，强装镇定）你、你是谁啊？为什么会在这里？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（冷淡，上下打量她）这句话应该我问你。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（不服气）我... 我是来探险的！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（皱眉）探险？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（挺胸）对！听说这里闹鬼，我来看看是不是真的。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（冷淡）无聊。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（生气）喂！你什么意思啊！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（不理她，继续往前走）这里不是你该来的地方，赶紧走。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（更生气了）你凭什么管我啊！你又是谁？为什么会在这里？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（冷淡）我来调查一些事情。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（好奇）调查？调查什么？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（回头看了她一眼）和你无关。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（害怕）那、那是什么声音？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（皱眉，表情严肃） ...</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（紧张）该不会... 真的有鬼吧？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（冷淡）世界上没有鬼。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> （小声）那你说是什么...</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（着急）喂！你去哪儿？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（头也不回）上去看看。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（纠结）等、等一下啊！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="22">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -477,357 +524,35 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9.8"/>
+      <sz val="9.8000000000000007"/>
       <color rgb="FFC9A26D"/>
       <name val="JetBrains Mono"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="8"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="9"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -835,251 +560,9 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1091,61 +574,17 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1403,26 +842,26 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:V108"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
-    <col min="2" max="2" width="66.5583333333333" customWidth="1"/>
-    <col min="4" max="4" width="20.8833333333333" customWidth="1"/>
-    <col min="7" max="7" width="15.8833333333333" customWidth="1"/>
-    <col min="8" max="8" width="13.6666666666667" customWidth="1"/>
-    <col min="9" max="9" width="15.775" customWidth="1"/>
-    <col min="10" max="10" width="13.2166666666667" customWidth="1"/>
-    <col min="11" max="11" width="16.2166666666667" customWidth="1"/>
-    <col min="12" max="12" width="13.3333333333333" customWidth="1"/>
-    <col min="15" max="15" width="13.6666666666667" customWidth="1"/>
-    <col min="17" max="17" width="11.775" customWidth="1"/>
-    <col min="18" max="18" width="11.5583333333333" customWidth="1"/>
+    <col min="2" max="2" width="66.5546875" customWidth="1"/>
+    <col min="4" max="4" width="20.88671875" customWidth="1"/>
+    <col min="7" max="7" width="15.88671875" customWidth="1"/>
+    <col min="8" max="8" width="13.6640625" customWidth="1"/>
+    <col min="9" max="9" width="15.77734375" customWidth="1"/>
+    <col min="10" max="10" width="13.21875" customWidth="1"/>
+    <col min="11" max="11" width="16.21875" customWidth="1"/>
+    <col min="12" max="12" width="13.33203125" customWidth="1"/>
+    <col min="15" max="15" width="13.6640625" customWidth="1"/>
+    <col min="17" max="17" width="11.77734375" customWidth="1"/>
+    <col min="18" max="18" width="11.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22">
@@ -1514,6 +953,9 @@
       <c r="E3">
         <v>1</v>
       </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
       <c r="G3" s="1" t="s">
         <v>26</v>
       </c>
@@ -1521,7 +963,7 @@
         <v>22</v>
       </c>
       <c r="J3">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="K3" t="s">
         <v>27</v>
@@ -1543,11 +985,14 @@
       <c r="R4">
         <v>1</v>
       </c>
+      <c r="S4">
+        <v>1</v>
+      </c>
       <c r="T4">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U4">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -1563,11 +1008,14 @@
       <c r="R5">
         <v>1</v>
       </c>
+      <c r="S5">
+        <v>1</v>
+      </c>
       <c r="T5">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U5">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -1583,11 +1031,14 @@
       <c r="R6">
         <v>1</v>
       </c>
+      <c r="S6">
+        <v>1</v>
+      </c>
       <c r="T6">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U6">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -1595,7 +1046,7 @@
         <v>28</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>31</v>
+        <v>86</v>
       </c>
       <c r="C7" t="s">
         <v>27</v>
@@ -1603,11 +1054,14 @@
       <c r="R7">
         <v>1</v>
       </c>
+      <c r="S7">
+        <v>1</v>
+      </c>
       <c r="T7">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U7">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -1615,7 +1069,7 @@
         <v>23</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C8" t="s">
         <v>25</v>
@@ -1623,11 +1077,14 @@
       <c r="R8">
         <v>1</v>
       </c>
+      <c r="S8">
+        <v>1</v>
+      </c>
       <c r="T8">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U8">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -1635,7 +1092,7 @@
         <v>28</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>33</v>
+        <v>87</v>
       </c>
       <c r="C9" t="s">
         <v>27</v>
@@ -1643,11 +1100,14 @@
       <c r="R9">
         <v>1</v>
       </c>
+      <c r="S9">
+        <v>1</v>
+      </c>
       <c r="T9">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U9">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1655,7 +1115,7 @@
         <v>23</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C10" t="s">
         <v>25</v>
@@ -1663,11 +1123,14 @@
       <c r="R10">
         <v>1</v>
       </c>
+      <c r="S10">
+        <v>1</v>
+      </c>
       <c r="T10">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U10">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1675,7 +1138,7 @@
         <v>28</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>35</v>
+        <v>88</v>
       </c>
       <c r="C11" t="s">
         <v>27</v>
@@ -1683,11 +1146,14 @@
       <c r="R11">
         <v>1</v>
       </c>
+      <c r="S11">
+        <v>1</v>
+      </c>
       <c r="T11">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U11">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1695,7 +1161,7 @@
         <v>23</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C12" t="s">
         <v>25</v>
@@ -1703,11 +1169,14 @@
       <c r="R12">
         <v>1</v>
       </c>
+      <c r="S12">
+        <v>1</v>
+      </c>
       <c r="T12">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U12">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1715,7 +1184,7 @@
         <v>28</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>37</v>
+        <v>89</v>
       </c>
       <c r="C13" t="s">
         <v>27</v>
@@ -1723,11 +1192,14 @@
       <c r="R13">
         <v>1</v>
       </c>
+      <c r="S13">
+        <v>1</v>
+      </c>
       <c r="T13">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U13">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -1735,7 +1207,7 @@
         <v>23</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
         <v>25</v>
@@ -1743,11 +1215,14 @@
       <c r="R14">
         <v>1</v>
       </c>
+      <c r="S14">
+        <v>1</v>
+      </c>
       <c r="T14">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U14">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1755,7 +1230,7 @@
         <v>28</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
         <v>27</v>
@@ -1763,11 +1238,14 @@
       <c r="R15">
         <v>1</v>
       </c>
+      <c r="S15">
+        <v>1</v>
+      </c>
       <c r="T15">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U15">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -1775,7 +1253,7 @@
         <v>23</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C16" t="s">
         <v>25</v>
@@ -1783,11 +1261,14 @@
       <c r="R16">
         <v>1</v>
       </c>
+      <c r="S16">
+        <v>1</v>
+      </c>
       <c r="T16">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U16">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="17" spans="1:21">
@@ -1795,7 +1276,7 @@
         <v>28</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="C17" t="s">
         <v>27</v>
@@ -1803,11 +1284,14 @@
       <c r="R17">
         <v>1</v>
       </c>
+      <c r="S17">
+        <v>1</v>
+      </c>
       <c r="T17">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U17">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="18" spans="1:21">
@@ -1815,7 +1299,7 @@
         <v>23</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C18" t="s">
         <v>25</v>
@@ -1823,11 +1307,14 @@
       <c r="R18">
         <v>1</v>
       </c>
+      <c r="S18">
+        <v>1</v>
+      </c>
       <c r="T18">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U18">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="19" spans="1:21">
@@ -1835,7 +1322,7 @@
         <v>28</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>43</v>
+        <v>91</v>
       </c>
       <c r="C19" t="s">
         <v>27</v>
@@ -1843,11 +1330,14 @@
       <c r="R19">
         <v>1</v>
       </c>
+      <c r="S19">
+        <v>1</v>
+      </c>
       <c r="T19">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U19">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="20" spans="1:21">
@@ -1855,7 +1345,7 @@
         <v>23</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C20" t="s">
         <v>25</v>
@@ -1863,11 +1353,14 @@
       <c r="R20">
         <v>1</v>
       </c>
+      <c r="S20">
+        <v>1</v>
+      </c>
       <c r="T20">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U20">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="21" spans="1:21">
@@ -1875,7 +1368,7 @@
         <v>28</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C21" t="s">
         <v>27</v>
@@ -1884,11 +1377,14 @@
       <c r="R21">
         <v>1</v>
       </c>
+      <c r="S21">
+        <v>1</v>
+      </c>
       <c r="T21">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U21">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -1896,7 +1392,7 @@
         <v>23</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C22" t="s">
         <v>25</v>
@@ -1909,19 +1405,22 @@
         <v>22</v>
       </c>
       <c r="M22">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
       <c r="N22" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="R22">
         <v>1</v>
       </c>
+      <c r="S22">
+        <v>1</v>
+      </c>
       <c r="T22">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U22">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -1929,7 +1428,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C23" t="s">
         <v>25</v>
@@ -1937,31 +1436,37 @@
       <c r="R23">
         <v>2</v>
       </c>
+      <c r="S23">
+        <v>1</v>
+      </c>
       <c r="T23">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U23">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="24" spans="1:21">
       <c r="A24" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>50</v>
+        <v>92</v>
       </c>
       <c r="C24" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="R24">
         <v>2</v>
       </c>
+      <c r="S24">
+        <v>1</v>
+      </c>
       <c r="T24">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U24">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="25" spans="1:21">
@@ -1969,7 +1474,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="C25" t="s">
         <v>25</v>
@@ -1977,11 +1482,14 @@
       <c r="R25">
         <v>2</v>
       </c>
+      <c r="S25">
+        <v>1</v>
+      </c>
       <c r="T25">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U25">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="26" spans="1:21">
@@ -1989,7 +1497,7 @@
         <v>28</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>52</v>
+        <v>93</v>
       </c>
       <c r="C26" t="s">
         <v>27</v>
@@ -1997,31 +1505,37 @@
       <c r="R26">
         <v>2</v>
       </c>
+      <c r="S26">
+        <v>1</v>
+      </c>
       <c r="T26">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U26">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="27" spans="1:21">
       <c r="A27" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>53</v>
+        <v>94</v>
       </c>
       <c r="C27" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="R27">
         <v>2</v>
       </c>
+      <c r="S27">
+        <v>1</v>
+      </c>
       <c r="T27">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U27">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="28" spans="1:21">
@@ -2029,7 +1543,7 @@
         <v>28</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C28" t="s">
         <v>27</v>
@@ -2037,31 +1551,37 @@
       <c r="R28">
         <v>2</v>
       </c>
+      <c r="S28">
+        <v>1</v>
+      </c>
       <c r="T28">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U28">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="29" spans="1:21">
       <c r="A29" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="C29" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="R29">
         <v>2</v>
       </c>
+      <c r="S29">
+        <v>1</v>
+      </c>
       <c r="T29">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U29">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="30" spans="1:21">
@@ -2069,7 +1589,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="C30" t="s">
         <v>27</v>
@@ -2077,11 +1597,14 @@
       <c r="R30">
         <v>2</v>
       </c>
+      <c r="S30">
+        <v>1</v>
+      </c>
       <c r="T30">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U30">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="31" spans="1:21">
@@ -2089,7 +1612,7 @@
         <v>23</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="C31" t="s">
         <v>25</v>
@@ -2097,31 +1620,37 @@
       <c r="R31">
         <v>2</v>
       </c>
+      <c r="S31">
+        <v>1</v>
+      </c>
       <c r="T31">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U31">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="32" spans="1:21">
       <c r="A32" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C32" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="R32">
         <v>2</v>
       </c>
+      <c r="S32">
+        <v>1</v>
+      </c>
       <c r="T32">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U32">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="33" spans="1:21">
@@ -2129,7 +1658,7 @@
         <v>23</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="C33" t="s">
         <v>25</v>
@@ -2137,31 +1666,37 @@
       <c r="R33">
         <v>2</v>
       </c>
+      <c r="S33">
+        <v>1</v>
+      </c>
       <c r="T33">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U33">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="34" spans="1:21">
       <c r="A34" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="C34" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="R34">
         <v>2</v>
       </c>
+      <c r="S34">
+        <v>1</v>
+      </c>
       <c r="T34">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U34">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="35" spans="1:21">
@@ -2169,7 +1704,7 @@
         <v>28</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="C35" t="s">
         <v>27</v>
@@ -2177,31 +1712,37 @@
       <c r="R35">
         <v>2</v>
       </c>
+      <c r="S35">
+        <v>1</v>
+      </c>
       <c r="T35">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U35">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="36" spans="1:21">
       <c r="A36" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>62</v>
+        <v>99</v>
       </c>
       <c r="C36" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="R36">
         <v>2</v>
       </c>
+      <c r="S36">
+        <v>1</v>
+      </c>
       <c r="T36">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U36">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="37" spans="1:21">
@@ -2209,7 +1750,7 @@
         <v>28</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="C37" t="s">
         <v>27</v>
@@ -2217,31 +1758,37 @@
       <c r="R37">
         <v>2</v>
       </c>
+      <c r="S37">
+        <v>1</v>
+      </c>
       <c r="T37">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U37">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="38" spans="1:21">
       <c r="A38" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="C38" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="R38">
         <v>2</v>
       </c>
+      <c r="S38">
+        <v>1</v>
+      </c>
       <c r="T38">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U38">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="39" spans="1:21">
@@ -2249,7 +1796,7 @@
         <v>28</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>65</v>
+        <v>102</v>
       </c>
       <c r="C39" t="s">
         <v>27</v>
@@ -2257,11 +1804,14 @@
       <c r="R39">
         <v>2</v>
       </c>
+      <c r="S39">
+        <v>1</v>
+      </c>
       <c r="T39">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U39">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="40" spans="1:21">
@@ -2269,7 +1819,7 @@
         <v>23</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="C40" t="s">
         <v>25</v>
@@ -2280,11 +1830,14 @@
       <c r="R40">
         <v>2</v>
       </c>
+      <c r="S40">
+        <v>1</v>
+      </c>
       <c r="T40">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U40">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="41" spans="1:21">
@@ -2292,7 +1845,7 @@
         <v>23</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="C41" t="s">
         <v>25</v>
@@ -2300,42 +1853,48 @@
       <c r="R41">
         <v>2</v>
       </c>
+      <c r="S41">
+        <v>1</v>
+      </c>
       <c r="T41">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U41">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="42" spans="1:21">
       <c r="A42" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>68</v>
+        <v>103</v>
       </c>
       <c r="C42" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="R42">
         <v>2</v>
       </c>
+      <c r="S42">
+        <v>1</v>
+      </c>
       <c r="T42">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U42">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="43" spans="1:21">
       <c r="A43" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>68</v>
+        <v>103</v>
       </c>
       <c r="C43" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>22</v>
@@ -2349,11 +1908,14 @@
       <c r="R43">
         <v>2</v>
       </c>
+      <c r="S43">
+        <v>1</v>
+      </c>
       <c r="T43">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U43">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="44" spans="1:21">
@@ -2361,7 +1923,7 @@
         <v>23</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="C44" t="s">
         <v>25</v>
@@ -2369,6 +1931,9 @@
       <c r="E44">
         <v>3</v>
       </c>
+      <c r="F44">
+        <v>2</v>
+      </c>
       <c r="G44" s="1" t="s">
         <v>26</v>
       </c>
@@ -2376,7 +1941,7 @@
         <v>22</v>
       </c>
       <c r="J44">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="K44" t="s">
         <v>27</v>
@@ -2384,11 +1949,14 @@
       <c r="R44">
         <v>2</v>
       </c>
+      <c r="S44">
+        <v>1</v>
+      </c>
       <c r="T44">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U44">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="45" spans="1:21">
@@ -2396,7 +1964,7 @@
         <v>28</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>70</v>
+        <v>104</v>
       </c>
       <c r="C45" t="s">
         <v>27</v>
@@ -2404,11 +1972,14 @@
       <c r="R45">
         <v>3</v>
       </c>
+      <c r="S45">
+        <v>2</v>
+      </c>
       <c r="T45">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U45">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="46" spans="1:21">
@@ -2416,7 +1987,7 @@
         <v>23</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="C46" t="s">
         <v>25</v>
@@ -2424,11 +1995,14 @@
       <c r="R46">
         <v>3</v>
       </c>
+      <c r="S46">
+        <v>2</v>
+      </c>
       <c r="T46">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U46">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="47" spans="1:21">
@@ -2436,7 +2010,7 @@
         <v>28</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="C47" t="s">
         <v>27</v>
@@ -2444,11 +2018,14 @@
       <c r="R47">
         <v>3</v>
       </c>
+      <c r="S47">
+        <v>2</v>
+      </c>
       <c r="T47">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U47">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="48" spans="1:21">
@@ -2456,7 +2033,7 @@
         <v>23</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="C48" t="s">
         <v>25</v>
@@ -2464,11 +2041,14 @@
       <c r="R48">
         <v>3</v>
       </c>
+      <c r="S48">
+        <v>2</v>
+      </c>
       <c r="T48">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U48">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="49" spans="1:21">
@@ -2476,7 +2056,7 @@
         <v>28</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="C49" t="s">
         <v>27</v>
@@ -2484,11 +2064,14 @@
       <c r="R49">
         <v>3</v>
       </c>
+      <c r="S49">
+        <v>2</v>
+      </c>
       <c r="T49">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U49">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="50" spans="1:21">
@@ -2496,7 +2079,7 @@
         <v>23</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="C50" t="s">
         <v>25</v>
@@ -2504,11 +2087,14 @@
       <c r="R50">
         <v>3</v>
       </c>
+      <c r="S50">
+        <v>2</v>
+      </c>
       <c r="T50">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U50">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="51" spans="1:21">
@@ -2516,7 +2102,7 @@
         <v>28</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>76</v>
+        <v>107</v>
       </c>
       <c r="C51" t="s">
         <v>27</v>
@@ -2524,11 +2110,14 @@
       <c r="R51">
         <v>3</v>
       </c>
+      <c r="S51">
+        <v>2</v>
+      </c>
       <c r="T51">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U51">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="52" spans="1:21">
@@ -2536,7 +2125,7 @@
         <v>23</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="C52" t="s">
         <v>25</v>
@@ -2544,11 +2133,14 @@
       <c r="R52">
         <v>3</v>
       </c>
+      <c r="S52">
+        <v>2</v>
+      </c>
       <c r="T52">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U52">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="53" spans="1:21">
@@ -2556,7 +2148,7 @@
         <v>28</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="C53" t="s">
         <v>27</v>
@@ -2564,11 +2156,14 @@
       <c r="R53">
         <v>3</v>
       </c>
+      <c r="S53">
+        <v>2</v>
+      </c>
       <c r="T53">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U53">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="54" spans="1:21">
@@ -2576,7 +2171,7 @@
         <v>23</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>79</v>
+        <v>56</v>
       </c>
       <c r="C54" t="s">
         <v>25</v>
@@ -2587,11 +2182,14 @@
       <c r="R54">
         <v>3</v>
       </c>
+      <c r="S54">
+        <v>2</v>
+      </c>
       <c r="T54">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U54">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="55" spans="1:21">
@@ -2599,7 +2197,7 @@
         <v>23</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="C55" t="s">
         <v>25</v>
@@ -2611,7 +2209,7 @@
         <v>22</v>
       </c>
       <c r="J55">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="K55" t="s">
         <v>27</v>
@@ -2619,11 +2217,14 @@
       <c r="R55">
         <v>3</v>
       </c>
+      <c r="S55">
+        <v>2</v>
+      </c>
       <c r="T55">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U55">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="56" spans="1:21">
@@ -2631,7 +2232,7 @@
         <v>28</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="C56" t="s">
         <v>27</v>
@@ -2639,11 +2240,14 @@
       <c r="R56">
         <v>4</v>
       </c>
+      <c r="S56">
+        <v>2</v>
+      </c>
       <c r="T56">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U56">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="57" spans="1:21">
@@ -2651,7 +2255,7 @@
         <v>23</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="C57" t="s">
         <v>25</v>
@@ -2659,11 +2263,14 @@
       <c r="R57">
         <v>4</v>
       </c>
+      <c r="S57">
+        <v>2</v>
+      </c>
       <c r="T57">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U57">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="58" spans="1:21">
@@ -2671,7 +2278,7 @@
         <v>23</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="C58" t="s">
         <v>25</v>
@@ -2679,11 +2286,14 @@
       <c r="R58">
         <v>4</v>
       </c>
+      <c r="S58">
+        <v>2</v>
+      </c>
       <c r="T58">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U58">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="59" spans="1:21">
@@ -2691,7 +2301,7 @@
         <v>28</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>84</v>
+        <v>110</v>
       </c>
       <c r="C59" t="s">
         <v>27</v>
@@ -2699,11 +2309,14 @@
       <c r="R59">
         <v>4</v>
       </c>
+      <c r="S59">
+        <v>2</v>
+      </c>
       <c r="T59">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U59">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="60" spans="1:21">
@@ -2711,7 +2324,7 @@
         <v>23</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="C60" t="s">
         <v>25</v>
@@ -2719,11 +2332,14 @@
       <c r="R60">
         <v>4</v>
       </c>
+      <c r="S60">
+        <v>2</v>
+      </c>
       <c r="T60">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U60">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="61" spans="1:21">
@@ -2731,7 +2347,7 @@
         <v>28</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="C61" t="s">
         <v>27</v>
@@ -2739,11 +2355,14 @@
       <c r="R61">
         <v>4</v>
       </c>
+      <c r="S61">
+        <v>2</v>
+      </c>
       <c r="T61">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U61">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="62" spans="1:21">
@@ -2751,7 +2370,7 @@
         <v>23</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="C62" t="s">
         <v>25</v>
@@ -2759,11 +2378,14 @@
       <c r="R62">
         <v>4</v>
       </c>
+      <c r="S62">
+        <v>2</v>
+      </c>
       <c r="T62">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U62">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="63" spans="1:21">
@@ -2771,7 +2393,7 @@
         <v>23</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="C63" t="s">
         <v>25</v>
@@ -2779,11 +2401,14 @@
       <c r="R63">
         <v>4</v>
       </c>
+      <c r="S63">
+        <v>2</v>
+      </c>
       <c r="T63">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U63">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="64" spans="1:21">
@@ -2791,7 +2416,7 @@
         <v>28</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="C64" t="s">
         <v>27</v>
@@ -2799,11 +2424,14 @@
       <c r="R64">
         <v>4</v>
       </c>
+      <c r="S64">
+        <v>2</v>
+      </c>
       <c r="T64">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U64">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="65" spans="1:21">
@@ -2811,7 +2439,7 @@
         <v>23</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="C65" t="s">
         <v>25</v>
@@ -2819,11 +2447,14 @@
       <c r="R65">
         <v>4</v>
       </c>
+      <c r="S65">
+        <v>2</v>
+      </c>
       <c r="T65">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U65">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="66" spans="1:21">
@@ -2831,7 +2462,7 @@
         <v>23</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>91</v>
+        <v>64</v>
       </c>
       <c r="C66" t="s">
         <v>25</v>
@@ -2839,11 +2470,14 @@
       <c r="R66">
         <v>4</v>
       </c>
+      <c r="S66">
+        <v>2</v>
+      </c>
       <c r="T66">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U66">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="67" spans="1:21">
@@ -2851,7 +2485,7 @@
         <v>28</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="C67" t="s">
         <v>27</v>
@@ -2859,11 +2493,14 @@
       <c r="R67">
         <v>4</v>
       </c>
+      <c r="S67">
+        <v>2</v>
+      </c>
       <c r="T67">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U67">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="68" spans="1:21">
@@ -2871,7 +2508,7 @@
         <v>23</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>93</v>
+        <v>65</v>
       </c>
       <c r="C68" t="s">
         <v>25</v>
@@ -2879,11 +2516,14 @@
       <c r="R68">
         <v>4</v>
       </c>
+      <c r="S68">
+        <v>2</v>
+      </c>
       <c r="T68">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U68">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="69" spans="1:21">
@@ -2891,7 +2531,7 @@
         <v>23</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="C69" t="s">
         <v>25</v>
@@ -2899,11 +2539,14 @@
       <c r="R69">
         <v>4</v>
       </c>
+      <c r="S69">
+        <v>2</v>
+      </c>
       <c r="T69">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U69">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="70" spans="1:21">
@@ -2911,7 +2554,7 @@
         <v>28</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="C70" t="s">
         <v>27</v>
@@ -2919,11 +2562,14 @@
       <c r="R70">
         <v>4</v>
       </c>
+      <c r="S70">
+        <v>2</v>
+      </c>
       <c r="T70">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U70">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="71" spans="1:21">
@@ -2931,7 +2577,7 @@
         <v>23</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="C71" t="s">
         <v>25</v>
@@ -2939,11 +2585,14 @@
       <c r="R71">
         <v>4</v>
       </c>
+      <c r="S71">
+        <v>2</v>
+      </c>
       <c r="T71">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U71">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="72" spans="1:21">
@@ -2951,7 +2600,7 @@
         <v>23</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="C72" t="s">
         <v>25</v>
@@ -2959,11 +2608,14 @@
       <c r="R72">
         <v>4</v>
       </c>
+      <c r="S72">
+        <v>2</v>
+      </c>
       <c r="T72">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U72">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="73" spans="1:21">
@@ -2971,7 +2623,7 @@
         <v>23</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="C73" t="s">
         <v>25</v>
@@ -2980,20 +2632,23 @@
         <v>22</v>
       </c>
       <c r="M73">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
       <c r="N73" t="s">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="O73" s="1"/>
       <c r="R73">
         <v>4</v>
       </c>
+      <c r="S73">
+        <v>2</v>
+      </c>
       <c r="T73">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U73">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="74" spans="1:21">
@@ -3001,7 +2656,7 @@
         <v>28</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="C74" t="s">
         <v>27</v>
@@ -3009,11 +2664,14 @@
       <c r="R74">
         <v>4</v>
       </c>
+      <c r="S74">
+        <v>2</v>
+      </c>
       <c r="T74">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U74">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="75" spans="1:21">
@@ -3021,7 +2679,7 @@
         <v>23</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="C75" t="s">
         <v>25</v>
@@ -3032,11 +2690,14 @@
       <c r="R75">
         <v>4</v>
       </c>
+      <c r="S75">
+        <v>2</v>
+      </c>
       <c r="T75">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U75">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="76" spans="1:21">
@@ -3044,7 +2705,7 @@
         <v>23</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>102</v>
+        <v>72</v>
       </c>
       <c r="C76" t="s">
         <v>25</v>
@@ -3052,31 +2713,37 @@
       <c r="R76">
         <v>4</v>
       </c>
+      <c r="S76">
+        <v>2</v>
+      </c>
       <c r="T76">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U76">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="77" spans="1:21">
       <c r="A77" t="s">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="C77" t="s">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="R77">
         <v>4</v>
       </c>
+      <c r="S77">
+        <v>2</v>
+      </c>
       <c r="T77">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U77">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="78" spans="1:21">
@@ -3084,7 +2751,7 @@
         <v>23</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>105</v>
+        <v>74</v>
       </c>
       <c r="C78" t="s">
         <v>25</v>
@@ -3092,31 +2759,37 @@
       <c r="R78">
         <v>4</v>
       </c>
+      <c r="S78">
+        <v>2</v>
+      </c>
       <c r="T78">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U78">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="79" spans="1:21">
       <c r="A79" t="s">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="C79" t="s">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="R79">
         <v>4</v>
       </c>
+      <c r="S79">
+        <v>2</v>
+      </c>
       <c r="T79">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U79">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="80" spans="1:21">
@@ -3124,7 +2797,7 @@
         <v>23</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>107</v>
+        <v>75</v>
       </c>
       <c r="C80" t="s">
         <v>25</v>
@@ -3133,7 +2806,7 @@
         <v>22</v>
       </c>
       <c r="J80">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="K80" t="s">
         <v>27</v>
@@ -3141,11 +2814,14 @@
       <c r="R80">
         <v>4</v>
       </c>
+      <c r="S80">
+        <v>2</v>
+      </c>
       <c r="T80">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U80">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="81" spans="1:21">
@@ -3153,7 +2829,7 @@
         <v>23</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>108</v>
+        <v>76</v>
       </c>
       <c r="C81" t="s">
         <v>25</v>
@@ -3161,11 +2837,14 @@
       <c r="R81">
         <v>4</v>
       </c>
+      <c r="S81">
+        <v>2</v>
+      </c>
       <c r="T81">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U81">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="82" spans="1:21">
@@ -3173,7 +2852,7 @@
         <v>28</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="C82" t="s">
         <v>27</v>
@@ -3181,31 +2860,37 @@
       <c r="R82">
         <v>4</v>
       </c>
+      <c r="S82">
+        <v>2</v>
+      </c>
       <c r="T82">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U82">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="83" spans="1:21">
       <c r="A83" t="s">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="C83" t="s">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="R83">
         <v>4</v>
       </c>
+      <c r="S83">
+        <v>2</v>
+      </c>
       <c r="T83">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U83">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="84" spans="1:21">
@@ -3213,7 +2898,7 @@
         <v>28</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="C84" t="s">
         <v>27</v>
@@ -3221,31 +2906,37 @@
       <c r="R84">
         <v>4</v>
       </c>
+      <c r="S84">
+        <v>2</v>
+      </c>
       <c r="T84">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U84">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="85" spans="1:21">
       <c r="A85" t="s">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="C85" t="s">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="R85">
         <v>4</v>
       </c>
+      <c r="S85">
+        <v>2</v>
+      </c>
       <c r="T85">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U85">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="86" spans="1:21">
@@ -3253,7 +2944,7 @@
         <v>28</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="C86" t="s">
         <v>27</v>
@@ -3261,31 +2952,37 @@
       <c r="R86">
         <v>4</v>
       </c>
+      <c r="S86">
+        <v>2</v>
+      </c>
       <c r="T86">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U86">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="87" spans="1:21">
       <c r="A87" t="s">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C87" t="s">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="R87">
         <v>4</v>
       </c>
+      <c r="S87">
+        <v>2</v>
+      </c>
       <c r="T87">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U87">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="88" spans="1:21">
@@ -3293,7 +2990,7 @@
         <v>28</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C88" t="s">
         <v>27</v>
@@ -3301,31 +2998,37 @@
       <c r="R88">
         <v>4</v>
       </c>
+      <c r="S88">
+        <v>2</v>
+      </c>
       <c r="T88">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U88">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="89" spans="1:21">
       <c r="A89" t="s">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="C89" t="s">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="R89">
         <v>4</v>
       </c>
+      <c r="S89">
+        <v>2</v>
+      </c>
       <c r="T89">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U89">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="90" spans="1:21">
@@ -3333,7 +3036,7 @@
         <v>28</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="C90" t="s">
         <v>27</v>
@@ -3341,11 +3044,14 @@
       <c r="R90">
         <v>4</v>
       </c>
+      <c r="S90">
+        <v>2</v>
+      </c>
       <c r="T90">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U90">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="91" spans="1:21">
@@ -3353,7 +3059,7 @@
         <v>23</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>118</v>
+        <v>77</v>
       </c>
       <c r="C91" t="s">
         <v>25</v>
@@ -3361,31 +3067,37 @@
       <c r="R91">
         <v>4</v>
       </c>
+      <c r="S91">
+        <v>2</v>
+      </c>
       <c r="T91">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U91">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="92" spans="1:21">
       <c r="A92" t="s">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="C92" t="s">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="R92">
         <v>4</v>
       </c>
+      <c r="S92">
+        <v>2</v>
+      </c>
       <c r="T92">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U92">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="93" spans="1:21">
@@ -3393,7 +3105,7 @@
         <v>28</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C93" t="s">
         <v>27</v>
@@ -3401,31 +3113,37 @@
       <c r="R93">
         <v>4</v>
       </c>
+      <c r="S93">
+        <v>2</v>
+      </c>
       <c r="T93">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U93">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="94" spans="1:21">
       <c r="A94" t="s">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="C94" t="s">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="R94">
         <v>4</v>
       </c>
+      <c r="S94">
+        <v>2</v>
+      </c>
       <c r="T94">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U94">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="95" spans="1:21">
@@ -3433,7 +3151,7 @@
         <v>23</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>122</v>
+        <v>78</v>
       </c>
       <c r="C95" t="s">
         <v>25</v>
@@ -3441,11 +3159,14 @@
       <c r="R95">
         <v>4</v>
       </c>
+      <c r="S95">
+        <v>2</v>
+      </c>
       <c r="T95">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U95">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="96" spans="1:21">
@@ -3453,7 +3174,7 @@
         <v>23</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>123</v>
+        <v>79</v>
       </c>
       <c r="C96" t="s">
         <v>25</v>
@@ -3461,11 +3182,14 @@
       <c r="R96">
         <v>4</v>
       </c>
+      <c r="S96">
+        <v>2</v>
+      </c>
       <c r="T96">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U96">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="97" spans="1:21">
@@ -3473,7 +3197,7 @@
         <v>28</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="C97" t="s">
         <v>27</v>
@@ -3481,31 +3205,37 @@
       <c r="R97">
         <v>4</v>
       </c>
+      <c r="S97">
+        <v>2</v>
+      </c>
       <c r="T97">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U97">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="98" spans="1:21">
       <c r="A98" t="s">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="C98" t="s">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="R98">
         <v>4</v>
       </c>
+      <c r="S98">
+        <v>2</v>
+      </c>
       <c r="T98">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U98">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="99" spans="1:21">
@@ -3513,7 +3243,7 @@
         <v>23</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>126</v>
+        <v>80</v>
       </c>
       <c r="C99" t="s">
         <v>25</v>
@@ -3521,11 +3251,14 @@
       <c r="R99">
         <v>4</v>
       </c>
+      <c r="S99">
+        <v>2</v>
+      </c>
       <c r="T99">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U99">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="100" spans="1:21">
@@ -3533,7 +3266,7 @@
         <v>28</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="C100" t="s">
         <v>27</v>
@@ -3541,31 +3274,37 @@
       <c r="R100">
         <v>4</v>
       </c>
+      <c r="S100">
+        <v>2</v>
+      </c>
       <c r="T100">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U100">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="101" spans="1:21">
       <c r="A101" t="s">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="C101" t="s">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="R101">
         <v>4</v>
       </c>
+      <c r="S101">
+        <v>2</v>
+      </c>
       <c r="T101">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U101">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="102" spans="1:21">
@@ -3573,7 +3312,7 @@
         <v>28</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C102" t="s">
         <v>27</v>
@@ -3581,11 +3320,14 @@
       <c r="R102">
         <v>4</v>
       </c>
+      <c r="S102">
+        <v>2</v>
+      </c>
       <c r="T102">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U102">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="103" spans="1:21">
@@ -3593,7 +3335,7 @@
         <v>23</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>130</v>
+        <v>81</v>
       </c>
       <c r="C103" t="s">
         <v>25</v>
@@ -3601,11 +3343,14 @@
       <c r="R103">
         <v>4</v>
       </c>
+      <c r="S103">
+        <v>2</v>
+      </c>
       <c r="T103">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U103">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="104" spans="1:21">
@@ -3613,7 +3358,7 @@
         <v>28</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C104" t="s">
         <v>27</v>
@@ -3621,31 +3366,37 @@
       <c r="R104">
         <v>4</v>
       </c>
+      <c r="S104">
+        <v>2</v>
+      </c>
       <c r="T104">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U104">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="105" spans="1:21">
       <c r="A105" t="s">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C105" t="s">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="R105">
         <v>4</v>
       </c>
+      <c r="S105">
+        <v>2</v>
+      </c>
       <c r="T105">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U105">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="106" spans="1:21">
@@ -3653,7 +3404,7 @@
         <v>28</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C106" t="s">
         <v>27</v>
@@ -3661,11 +3412,14 @@
       <c r="R106">
         <v>4</v>
       </c>
+      <c r="S106">
+        <v>2</v>
+      </c>
       <c r="T106">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U106">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="107" spans="1:21">
@@ -3673,7 +3427,7 @@
         <v>23</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>134</v>
+        <v>82</v>
       </c>
       <c r="C107" t="s">
         <v>25</v>
@@ -3681,25 +3435,28 @@
       <c r="R107">
         <v>4</v>
       </c>
+      <c r="S107">
+        <v>2</v>
+      </c>
       <c r="T107">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U107">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
     <row r="108" spans="1:21">
       <c r="A108" t="s">
-        <v>135</v>
+        <v>83</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>136</v>
+        <v>84</v>
       </c>
       <c r="C108">
         <v>2</v>
       </c>
       <c r="D108" t="s">
-        <v>137</v>
+        <v>85</v>
       </c>
       <c r="E108">
         <v>3</v>
@@ -3707,16 +3464,19 @@
       <c r="R108">
         <v>4</v>
       </c>
+      <c r="S108">
+        <v>2</v>
+      </c>
       <c r="T108">
-        <v>-640.8301</v>
+        <v>-640.83010000000002</v>
       </c>
       <c r="U108">
-        <v>819.1699</v>
+        <v>819.16989999999998</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/TextGame project/Assets/Resources/Story/1.xlsx
+++ b/TextGame project/Assets/Resources/Story/1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Text-Game\TextGame project\Assets\Resources\Story\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33EFFFD3-FE20-4F23-A505-56E4B60AA68D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{080D227E-6C6C-4CBF-A293-5B4E768588FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1932,7 +1932,7 @@
         <v>3</v>
       </c>
       <c r="F44">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>26</v>
@@ -1973,7 +1973,7 @@
         <v>3</v>
       </c>
       <c r="S45">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T45">
         <v>-640.83010000000002</v>
@@ -1996,7 +1996,7 @@
         <v>3</v>
       </c>
       <c r="S46">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T46">
         <v>-640.83010000000002</v>
@@ -2019,7 +2019,7 @@
         <v>3</v>
       </c>
       <c r="S47">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T47">
         <v>-640.83010000000002</v>
@@ -2042,7 +2042,7 @@
         <v>3</v>
       </c>
       <c r="S48">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T48">
         <v>-640.83010000000002</v>
@@ -2065,7 +2065,7 @@
         <v>3</v>
       </c>
       <c r="S49">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T49">
         <v>-640.83010000000002</v>
@@ -2088,7 +2088,7 @@
         <v>3</v>
       </c>
       <c r="S50">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T50">
         <v>-640.83010000000002</v>
@@ -2111,7 +2111,7 @@
         <v>3</v>
       </c>
       <c r="S51">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T51">
         <v>-640.83010000000002</v>
@@ -2134,7 +2134,7 @@
         <v>3</v>
       </c>
       <c r="S52">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T52">
         <v>-640.83010000000002</v>
@@ -2157,7 +2157,7 @@
         <v>3</v>
       </c>
       <c r="S53">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T53">
         <v>-640.83010000000002</v>
@@ -2183,7 +2183,7 @@
         <v>3</v>
       </c>
       <c r="S54">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T54">
         <v>-640.83010000000002</v>
@@ -2218,7 +2218,7 @@
         <v>3</v>
       </c>
       <c r="S55">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T55">
         <v>-640.83010000000002</v>
@@ -2241,7 +2241,7 @@
         <v>4</v>
       </c>
       <c r="S56">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T56">
         <v>-640.83010000000002</v>
@@ -2264,7 +2264,7 @@
         <v>4</v>
       </c>
       <c r="S57">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T57">
         <v>-640.83010000000002</v>
@@ -2287,7 +2287,7 @@
         <v>4</v>
       </c>
       <c r="S58">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T58">
         <v>-640.83010000000002</v>
@@ -2310,7 +2310,7 @@
         <v>4</v>
       </c>
       <c r="S59">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T59">
         <v>-640.83010000000002</v>
@@ -2333,7 +2333,7 @@
         <v>4</v>
       </c>
       <c r="S60">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T60">
         <v>-640.83010000000002</v>
@@ -2356,7 +2356,7 @@
         <v>4</v>
       </c>
       <c r="S61">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T61">
         <v>-640.83010000000002</v>
@@ -2379,7 +2379,7 @@
         <v>4</v>
       </c>
       <c r="S62">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T62">
         <v>-640.83010000000002</v>
@@ -2402,7 +2402,7 @@
         <v>4</v>
       </c>
       <c r="S63">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T63">
         <v>-640.83010000000002</v>
@@ -2425,7 +2425,7 @@
         <v>4</v>
       </c>
       <c r="S64">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T64">
         <v>-640.83010000000002</v>
@@ -2448,7 +2448,7 @@
         <v>4</v>
       </c>
       <c r="S65">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T65">
         <v>-640.83010000000002</v>
@@ -2471,7 +2471,7 @@
         <v>4</v>
       </c>
       <c r="S66">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T66">
         <v>-640.83010000000002</v>
@@ -2494,7 +2494,7 @@
         <v>4</v>
       </c>
       <c r="S67">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T67">
         <v>-640.83010000000002</v>
@@ -2517,7 +2517,7 @@
         <v>4</v>
       </c>
       <c r="S68">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T68">
         <v>-640.83010000000002</v>
@@ -2540,7 +2540,7 @@
         <v>4</v>
       </c>
       <c r="S69">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T69">
         <v>-640.83010000000002</v>
@@ -2563,7 +2563,7 @@
         <v>4</v>
       </c>
       <c r="S70">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T70">
         <v>-640.83010000000002</v>
@@ -2586,7 +2586,7 @@
         <v>4</v>
       </c>
       <c r="S71">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T71">
         <v>-640.83010000000002</v>
@@ -2609,7 +2609,7 @@
         <v>4</v>
       </c>
       <c r="S72">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T72">
         <v>-640.83010000000002</v>
@@ -2628,6 +2628,9 @@
       <c r="C73" t="s">
         <v>25</v>
       </c>
+      <c r="F73">
+        <v>2</v>
+      </c>
       <c r="L73" s="1" t="s">
         <v>22</v>
       </c>
@@ -2642,7 +2645,7 @@
         <v>4</v>
       </c>
       <c r="S73">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T73">
         <v>-640.83010000000002</v>
@@ -3156,6 +3159,9 @@
       <c r="C95" t="s">
         <v>25</v>
       </c>
+      <c r="F95">
+        <v>5</v>
+      </c>
       <c r="R95">
         <v>4</v>
       </c>
@@ -3183,7 +3189,7 @@
         <v>4</v>
       </c>
       <c r="S96">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T96">
         <v>-640.83010000000002</v>
@@ -3206,7 +3212,7 @@
         <v>4</v>
       </c>
       <c r="S97">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T97">
         <v>-640.83010000000002</v>
@@ -3229,7 +3235,7 @@
         <v>4</v>
       </c>
       <c r="S98">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T98">
         <v>-640.83010000000002</v>
@@ -3252,7 +3258,7 @@
         <v>4</v>
       </c>
       <c r="S99">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T99">
         <v>-640.83010000000002</v>
@@ -3275,7 +3281,7 @@
         <v>4</v>
       </c>
       <c r="S100">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T100">
         <v>-640.83010000000002</v>
@@ -3298,7 +3304,7 @@
         <v>4</v>
       </c>
       <c r="S101">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T101">
         <v>-640.83010000000002</v>
@@ -3321,7 +3327,7 @@
         <v>4</v>
       </c>
       <c r="S102">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T102">
         <v>-640.83010000000002</v>
@@ -3344,7 +3350,7 @@
         <v>4</v>
       </c>
       <c r="S103">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T103">
         <v>-640.83010000000002</v>
@@ -3367,7 +3373,7 @@
         <v>4</v>
       </c>
       <c r="S104">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T104">
         <v>-640.83010000000002</v>
@@ -3390,7 +3396,7 @@
         <v>4</v>
       </c>
       <c r="S105">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T105">
         <v>-640.83010000000002</v>
@@ -3413,7 +3419,7 @@
         <v>4</v>
       </c>
       <c r="S106">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T106">
         <v>-640.83010000000002</v>
@@ -3436,7 +3442,7 @@
         <v>4</v>
       </c>
       <c r="S107">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T107">
         <v>-640.83010000000002</v>
@@ -3465,7 +3471,7 @@
         <v>4</v>
       </c>
       <c r="S108">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T108">
         <v>-640.83010000000002</v>

--- a/TextGame project/Assets/Resources/Story/1.xlsx
+++ b/TextGame project/Assets/Resources/Story/1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Text-Game\TextGame project\Assets\Resources\Story\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{080D227E-6C6C-4CBF-A293-5B4E768588FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4D97B15-12C8-4F96-83DF-E936B2C91D50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="141">
   <si>
     <t>Name</t>
   </si>
@@ -508,6 +508,18 @@
   </si>
   <si>
     <t>（纠结）等、等一下啊！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Qianye2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Qianye1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Qianye2</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -515,7 +527,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -543,6 +555,14 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -564,7 +584,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -573,6 +593,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2418,8 +2439,17 @@
       <c r="B64" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C64" t="s">
-        <v>27</v>
+      <c r="C64" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J64">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="K64" s="4" t="s">
+        <v>138</v>
       </c>
       <c r="R64">
         <v>4</v>
@@ -2487,8 +2517,8 @@
       <c r="B67" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C67" t="s">
-        <v>27</v>
+      <c r="C67" s="4" t="s">
+        <v>138</v>
       </c>
       <c r="R67">
         <v>4</v>
@@ -2556,8 +2586,8 @@
       <c r="B70" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="C70" t="s">
-        <v>27</v>
+      <c r="C70" s="4" t="s">
+        <v>138</v>
       </c>
       <c r="R70">
         <v>4</v>
@@ -2661,8 +2691,8 @@
       <c r="B74" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="C74" t="s">
-        <v>27</v>
+      <c r="C74" s="4" t="s">
+        <v>138</v>
       </c>
       <c r="R74">
         <v>4</v>
@@ -2811,8 +2841,8 @@
       <c r="J80">
         <v>-640.83010000000002</v>
       </c>
-      <c r="K80" t="s">
-        <v>27</v>
+      <c r="K80" s="4" t="s">
+        <v>140</v>
       </c>
       <c r="R80">
         <v>4</v>
@@ -2857,8 +2887,8 @@
       <c r="B82" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C82" t="s">
-        <v>27</v>
+      <c r="C82" s="4" t="s">
+        <v>138</v>
       </c>
       <c r="R82">
         <v>4</v>
@@ -2903,8 +2933,17 @@
       <c r="B84" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="C84" t="s">
-        <v>27</v>
+      <c r="C84" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J84">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="K84" s="4" t="s">
+        <v>139</v>
       </c>
       <c r="R84">
         <v>4</v>
@@ -2949,8 +2988,8 @@
       <c r="B86" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="C86" t="s">
-        <v>27</v>
+      <c r="C86" s="4" t="s">
+        <v>139</v>
       </c>
       <c r="R86">
         <v>4</v>
@@ -2995,8 +3034,8 @@
       <c r="B88" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C88" t="s">
-        <v>27</v>
+      <c r="C88" s="4" t="s">
+        <v>139</v>
       </c>
       <c r="R88">
         <v>4</v>
@@ -3041,8 +3080,8 @@
       <c r="B90" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="C90" t="s">
-        <v>27</v>
+      <c r="C90" s="4" t="s">
+        <v>139</v>
       </c>
       <c r="R90">
         <v>4</v>
@@ -3205,8 +3244,17 @@
       <c r="B97" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="C97" t="s">
-        <v>27</v>
+      <c r="C97" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="I97" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J97">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="K97" s="4" t="s">
+        <v>140</v>
       </c>
       <c r="R97">
         <v>4</v>
@@ -3274,8 +3322,8 @@
       <c r="B100" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="C100" t="s">
-        <v>27</v>
+      <c r="C100" s="4" t="s">
+        <v>138</v>
       </c>
       <c r="R100">
         <v>4</v>
@@ -3320,8 +3368,8 @@
       <c r="B102" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="C102" t="s">
-        <v>27</v>
+      <c r="C102" s="4" t="s">
+        <v>138</v>
       </c>
       <c r="R102">
         <v>4</v>
@@ -3366,8 +3414,8 @@
       <c r="B104" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="C104" t="s">
-        <v>27</v>
+      <c r="C104" s="4" t="s">
+        <v>138</v>
       </c>
       <c r="R104">
         <v>4</v>
@@ -3412,8 +3460,8 @@
       <c r="B106" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C106" t="s">
-        <v>27</v>
+      <c r="C106" s="4" t="s">
+        <v>138</v>
       </c>
       <c r="R106">
         <v>4</v>
